--- a/data/FY27Q1.xlsx
+++ b/data/FY27Q1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73E8BB29-F6ED-6347-9BD5-244207166101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38CD041E-3702-D94C-88DD-6BEFCBE54A57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15520" yWindow="680" windowWidth="18640" windowHeight="20300" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -1621,6 +1621,9 @@
       <c r="B6" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="C6" s="15">
+        <v>23</v>
+      </c>
       <c r="D6" s="33"/>
       <c r="E6" s="34"/>
       <c r="F6" s="34"/>
@@ -1632,7 +1635,7 @@
       <c r="L6" s="33"/>
       <c r="M6" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-23</v>
       </c>
       <c r="N6" s="12">
         <f t="shared" si="0"/>
@@ -4033,6 +4036,9 @@
       <c r="A17" s="14"/>
       <c r="B17" s="32" t="s">
         <v>20</v>
+      </c>
+      <c r="C17" s="1">
+        <v>26</v>
       </c>
       <c r="D17" s="35"/>
       <c r="E17" s="10"/>
@@ -4045,7 +4051,7 @@
       <c r="L17" s="35"/>
       <c r="M17" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-26</v>
       </c>
       <c r="N17" s="12">
         <f t="shared" si="0"/>
@@ -6450,6 +6456,9 @@
       <c r="A28" s="14"/>
       <c r="B28" s="32" t="s">
         <v>20</v>
+      </c>
+      <c r="C28" s="1">
+        <v>5</v>
       </c>
       <c r="D28" s="35"/>
       <c r="E28" s="10"/>
@@ -6462,7 +6471,7 @@
       <c r="L28" s="35"/>
       <c r="M28" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="N28" s="12">
         <f t="shared" si="0"/>
@@ -8867,6 +8876,9 @@
       <c r="A39" s="14"/>
       <c r="B39" s="32" t="s">
         <v>20</v>
+      </c>
+      <c r="C39" s="1">
+        <v>2</v>
       </c>
       <c r="D39" s="35"/>
       <c r="E39" s="10"/>
@@ -8879,7 +8891,7 @@
       <c r="L39" s="35"/>
       <c r="M39" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="N39" s="12">
         <f t="shared" si="0"/>
@@ -11292,6 +11304,9 @@
       <c r="A50" s="14"/>
       <c r="B50" s="32" t="s">
         <v>20</v>
+      </c>
+      <c r="C50" s="1">
+        <v>4</v>
       </c>
       <c r="D50" s="35"/>
       <c r="E50" s="10"/>
@@ -11304,7 +11319,7 @@
       <c r="L50" s="35"/>
       <c r="M50" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="N50" s="12">
         <f t="shared" si="0"/>

--- a/data/FY27Q1.xlsx
+++ b/data/FY27Q1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38CD041E-3702-D94C-88DD-6BEFCBE54A57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA5314C4-9DD8-404B-B559-055F868EE544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15520" yWindow="680" windowWidth="18640" windowHeight="20300" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="16760" yWindow="680" windowWidth="18640" windowHeight="20260" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="27Q1" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="32">
   <si>
     <t>總計</t>
   </si>
@@ -169,7 +169,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>0927~10/03</t>
+    <t>09/27~10/03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>27Q1W2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10/04~10/10</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -976,7 +984,9 @@
       </c>
       <c r="B1" s="26"/>
       <c r="D1" s="25"/>
-      <c r="I1" s="26"/>
+      <c r="I1" s="26" t="s">
+        <v>30</v>
+      </c>
       <c r="J1" s="26"/>
       <c r="L1" s="25"/>
       <c r="Q1" s="26"/>
@@ -1017,7 +1027,9 @@
       </c>
       <c r="B2" s="22"/>
       <c r="D2" s="21"/>
-      <c r="I2" s="23"/>
+      <c r="I2" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="K2" s="23"/>
       <c r="M2" s="23"/>
       <c r="O2" s="23"/>
@@ -1373,11 +1385,13 @@
       <c r="J5" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="K5" s="40"/>
+      <c r="K5" s="40">
+        <v>17034</v>
+      </c>
       <c r="L5" s="1"/>
       <c r="M5" s="10">
         <f t="shared" ref="M5:N60" si="0">K5-C5</f>
-        <v>-17575</v>
+        <v>-541</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" si="0"/>
@@ -1398,7 +1412,7 @@
       <c r="T5" s="1"/>
       <c r="U5" s="10">
         <f t="shared" ref="U5:U60" si="2">S5-K5</f>
-        <v>0</v>
+        <v>-17034</v>
       </c>
       <c r="V5" s="12">
         <f t="shared" ref="V5:V60" si="3">T5-L5</f>
@@ -1632,10 +1646,13 @@
       <c r="J6" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="K6" s="15">
+        <v>22</v>
+      </c>
       <c r="L6" s="33"/>
       <c r="M6" s="10">
         <f t="shared" si="0"/>
-        <v>-23</v>
+        <v>-1</v>
       </c>
       <c r="N6" s="12">
         <f t="shared" si="0"/>
@@ -1652,7 +1669,7 @@
       <c r="T6" s="33"/>
       <c r="U6" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="V6" s="12">
         <f t="shared" si="3"/>
@@ -1848,18 +1865,23 @@
       <c r="J7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="L7" s="12"/>
+      <c r="K7" s="10">
+        <v>500</v>
+      </c>
+      <c r="L7" s="12">
+        <v>569204</v>
+      </c>
       <c r="M7" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O7" s="11" t="e">
+        <v>120791</v>
+      </c>
+      <c r="O7" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.26937443829683794</v>
       </c>
       <c r="Q7" s="14"/>
       <c r="R7" s="13" t="s">
@@ -1868,15 +1890,15 @@
       <c r="T7" s="12"/>
       <c r="U7" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="V7" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W7" s="11" t="e">
+        <v>-569204</v>
+      </c>
+      <c r="W7" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y7" s="14"/>
       <c r="Z7" s="13" t="s">
@@ -2064,18 +2086,23 @@
       <c r="J8" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="L8" s="12"/>
+      <c r="K8" s="10">
+        <v>430</v>
+      </c>
+      <c r="L8" s="12">
+        <v>882812</v>
+      </c>
       <c r="M8" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O8" s="11" t="e">
+        <v>299927</v>
+      </c>
+      <c r="O8" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.51455604450277503</v>
       </c>
       <c r="Q8" s="14"/>
       <c r="R8" s="13" t="s">
@@ -2084,15 +2111,15 @@
       <c r="T8" s="12"/>
       <c r="U8" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-430</v>
       </c>
       <c r="V8" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W8" s="11" t="e">
+        <v>-882812</v>
+      </c>
+      <c r="W8" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y8" s="14"/>
       <c r="Z8" s="13" t="s">
@@ -2280,18 +2307,23 @@
       <c r="J9" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="L9" s="12"/>
+      <c r="K9" s="10">
+        <v>161</v>
+      </c>
+      <c r="L9" s="12">
+        <v>956562</v>
+      </c>
       <c r="M9" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="N9" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O9" s="11" t="e">
+        <v>52572</v>
+      </c>
+      <c r="O9" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>5.8155510569807188E-2</v>
       </c>
       <c r="Q9" s="14"/>
       <c r="R9" s="13" t="s">
@@ -2300,15 +2332,15 @@
       <c r="T9" s="12"/>
       <c r="U9" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-161</v>
       </c>
       <c r="V9" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W9" s="11" t="e">
+        <v>-956562</v>
+      </c>
+      <c r="W9" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y9" s="14"/>
       <c r="Z9" s="13" t="s">
@@ -2496,18 +2528,23 @@
       <c r="J10" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="L10" s="12"/>
+      <c r="K10" s="10">
+        <v>137</v>
+      </c>
+      <c r="L10" s="12">
+        <v>2066476</v>
+      </c>
       <c r="M10" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-28</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O10" s="11" t="e">
+        <v>-676857</v>
+      </c>
+      <c r="O10" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>-0.24672797651615755</v>
       </c>
       <c r="Q10" s="14"/>
       <c r="R10" s="13" t="s">
@@ -2516,15 +2553,15 @@
       <c r="T10" s="12"/>
       <c r="U10" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-137</v>
       </c>
       <c r="V10" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="11" t="e">
+        <v>-2066476</v>
+      </c>
+      <c r="W10" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y10" s="14"/>
       <c r="Z10" s="13" t="s">
@@ -2712,18 +2749,23 @@
       <c r="J11" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="L11" s="12"/>
+      <c r="K11" s="10">
+        <v>21</v>
+      </c>
+      <c r="L11" s="12">
+        <v>124470</v>
+      </c>
       <c r="M11" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N11" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O11" s="11" t="e">
+        <v>10490</v>
+      </c>
+      <c r="O11" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>9.2033690121073874E-2</v>
       </c>
       <c r="Q11" s="14"/>
       <c r="R11" s="13" t="s">
@@ -2732,15 +2774,15 @@
       <c r="T11" s="12"/>
       <c r="U11" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-21</v>
       </c>
       <c r="V11" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="11" t="e">
+        <v>-124470</v>
+      </c>
+      <c r="W11" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y11" s="14"/>
       <c r="Z11" s="13" t="s">
@@ -2928,18 +2970,23 @@
       <c r="J12" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="L12" s="12"/>
+      <c r="K12" s="10">
+        <v>89</v>
+      </c>
+      <c r="L12" s="12">
+        <v>3715738</v>
+      </c>
       <c r="M12" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O12" s="11" t="e">
+        <v>140062</v>
+      </c>
+      <c r="O12" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>3.9170774980730919E-2</v>
       </c>
       <c r="Q12" s="14"/>
       <c r="R12" s="13" t="s">
@@ -2948,15 +2995,15 @@
       <c r="T12" s="12"/>
       <c r="U12" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-89</v>
       </c>
       <c r="V12" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="11" t="e">
+        <v>-3715738</v>
+      </c>
+      <c r="W12" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y12" s="14"/>
       <c r="Z12" s="13" t="s">
@@ -3144,18 +3191,23 @@
       <c r="J13" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="L13" s="12"/>
+      <c r="K13" s="10">
+        <v>122</v>
+      </c>
+      <c r="L13" s="12">
+        <v>2705048</v>
+      </c>
       <c r="M13" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O13" s="11" t="e">
+        <v>-276095</v>
+      </c>
+      <c r="O13" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>-9.2613806181052027E-2</v>
       </c>
       <c r="Q13" s="14"/>
       <c r="R13" s="13" t="s">
@@ -3164,15 +3216,15 @@
       <c r="T13" s="12"/>
       <c r="U13" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-122</v>
       </c>
       <c r="V13" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="11" t="e">
+        <v>-2705048</v>
+      </c>
+      <c r="W13" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y13" s="14"/>
       <c r="Z13" s="13" t="s">
@@ -3360,18 +3412,23 @@
       <c r="J14" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="L14" s="12"/>
+      <c r="K14" s="10">
+        <v>517</v>
+      </c>
+      <c r="L14" s="12">
+        <v>21701050</v>
+      </c>
       <c r="M14" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-46</v>
       </c>
       <c r="N14" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O14" s="11" t="e">
+        <v>-1190420</v>
+      </c>
+      <c r="O14" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>-5.2002776580097304E-2</v>
       </c>
       <c r="Q14" s="14"/>
       <c r="R14" s="13" t="s">
@@ -3380,15 +3437,15 @@
       <c r="T14" s="12"/>
       <c r="U14" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-517</v>
       </c>
       <c r="V14" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="11" t="e">
+        <v>-21701050</v>
+      </c>
+      <c r="W14" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y14" s="14"/>
       <c r="Z14" s="13" t="s">
@@ -3577,19 +3634,23 @@
         <v>18</v>
       </c>
       <c r="J15" s="9"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="7"/>
+      <c r="K15" s="8">
+        <v>1977</v>
+      </c>
+      <c r="L15" s="7">
+        <v>32721360</v>
+      </c>
       <c r="M15" s="27">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N15" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O15" s="29" t="e">
+        <v>-1519530</v>
+      </c>
+      <c r="O15" s="29">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>-4.4377643221306454E-2</v>
       </c>
       <c r="Q15" s="9" t="s">
         <v>18</v>
@@ -3599,15 +3660,15 @@
       <c r="T15" s="7"/>
       <c r="U15" s="27">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-1977</v>
       </c>
       <c r="V15" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W15" s="29" t="e">
+        <v>-32721360</v>
+      </c>
+      <c r="W15" s="29">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y15" s="9" t="s">
         <v>18</v>
@@ -3807,10 +3868,13 @@
       <c r="J16" s="32" t="s">
         <v>19</v>
       </c>
+      <c r="K16" s="1">
+        <v>9228</v>
+      </c>
       <c r="L16" s="35"/>
       <c r="M16" s="10">
         <f t="shared" si="0"/>
-        <v>-10989</v>
+        <v>-1761</v>
       </c>
       <c r="N16" s="12">
         <f t="shared" si="0"/>
@@ -3829,7 +3893,7 @@
       <c r="T16" s="35"/>
       <c r="U16" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-9228</v>
       </c>
       <c r="V16" s="12">
         <f t="shared" si="3"/>
@@ -4048,10 +4112,13 @@
       <c r="J17" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="K17" s="1">
+        <v>26</v>
+      </c>
       <c r="L17" s="35"/>
       <c r="M17" s="10">
         <f t="shared" si="0"/>
-        <v>-26</v>
+        <v>0</v>
       </c>
       <c r="N17" s="12">
         <f t="shared" si="0"/>
@@ -4068,7 +4135,7 @@
       <c r="T17" s="35"/>
       <c r="U17" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-26</v>
       </c>
       <c r="V17" s="12">
         <f t="shared" si="3"/>
@@ -4268,18 +4335,23 @@
       <c r="J18" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="L18" s="12"/>
+      <c r="K18" s="10">
+        <v>214</v>
+      </c>
+      <c r="L18" s="12">
+        <v>218415</v>
+      </c>
       <c r="M18" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="N18" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O18" s="11" t="e">
+        <v>45505</v>
+      </c>
+      <c r="O18" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.26317159215776992</v>
       </c>
       <c r="Q18" s="14"/>
       <c r="R18" s="13" t="s">
@@ -4288,15 +4360,15 @@
       <c r="T18" s="12"/>
       <c r="U18" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-214</v>
       </c>
       <c r="V18" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W18" s="11" t="e">
+        <v>-218415</v>
+      </c>
+      <c r="W18" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y18" s="14"/>
       <c r="Z18" s="13" t="s">
@@ -4484,18 +4556,23 @@
       <c r="J19" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="L19" s="12"/>
+      <c r="K19" s="10">
+        <v>273</v>
+      </c>
+      <c r="L19" s="12">
+        <v>350306</v>
+      </c>
       <c r="M19" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N19" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O19" s="11" t="e">
+        <v>95197</v>
+      </c>
+      <c r="O19" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.37316206013899939</v>
       </c>
       <c r="Q19" s="14"/>
       <c r="R19" s="13" t="s">
@@ -4504,15 +4581,15 @@
       <c r="T19" s="12"/>
       <c r="U19" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-273</v>
       </c>
       <c r="V19" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W19" s="11" t="e">
+        <v>-350306</v>
+      </c>
+      <c r="W19" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y19" s="14"/>
       <c r="Z19" s="13" t="s">
@@ -4700,18 +4777,23 @@
       <c r="J20" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="L20" s="12"/>
+      <c r="K20" s="10">
+        <v>92</v>
+      </c>
+      <c r="L20" s="12">
+        <v>519863</v>
+      </c>
       <c r="M20" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N20" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O20" s="11" t="e">
+        <v>120015</v>
+      </c>
+      <c r="O20" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.30015155759188494</v>
       </c>
       <c r="Q20" s="14"/>
       <c r="R20" s="13" t="s">
@@ -4720,15 +4802,15 @@
       <c r="T20" s="12"/>
       <c r="U20" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-92</v>
       </c>
       <c r="V20" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W20" s="11" t="e">
+        <v>-519863</v>
+      </c>
+      <c r="W20" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y20" s="14"/>
       <c r="Z20" s="13" t="s">
@@ -4916,18 +4998,23 @@
       <c r="J21" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="L21" s="12"/>
+      <c r="K21" s="10">
+        <v>63</v>
+      </c>
+      <c r="L21" s="12">
+        <v>997333</v>
+      </c>
       <c r="M21" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N21" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O21" s="11" t="e">
+        <v>36914</v>
+      </c>
+      <c r="O21" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>3.843530792289615E-2</v>
       </c>
       <c r="Q21" s="14"/>
       <c r="R21" s="13" t="s">
@@ -4936,15 +5023,15 @@
       <c r="T21" s="12"/>
       <c r="U21" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-63</v>
       </c>
       <c r="V21" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W21" s="11" t="e">
+        <v>-997333</v>
+      </c>
+      <c r="W21" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y21" s="14"/>
       <c r="Z21" s="13" t="s">
@@ -5132,18 +5219,23 @@
       <c r="J22" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="12"/>
+      <c r="K22" s="10">
+        <v>12</v>
+      </c>
+      <c r="L22" s="12">
+        <v>80080</v>
+      </c>
       <c r="M22" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="N22" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O22" s="11" t="e">
+        <v>-97230</v>
+      </c>
+      <c r="O22" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>-0.54836162652980658</v>
       </c>
       <c r="Q22" s="14"/>
       <c r="R22" s="13" t="s">
@@ -5152,15 +5244,15 @@
       <c r="T22" s="12"/>
       <c r="U22" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="V22" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W22" s="11" t="e">
+        <v>-80080</v>
+      </c>
+      <c r="W22" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y22" s="14"/>
       <c r="Z22" s="13" t="s">
@@ -5348,18 +5440,23 @@
       <c r="J23" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="L23" s="12"/>
+      <c r="K23" s="10">
+        <v>19</v>
+      </c>
+      <c r="L23" s="12">
+        <v>633048</v>
+      </c>
       <c r="M23" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N23" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O23" s="11" t="e">
+        <v>-50666</v>
+      </c>
+      <c r="O23" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>-7.4104084456366265E-2</v>
       </c>
       <c r="Q23" s="14"/>
       <c r="R23" s="13" t="s">
@@ -5368,15 +5465,15 @@
       <c r="T23" s="12"/>
       <c r="U23" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="V23" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W23" s="11" t="e">
+        <v>-633048</v>
+      </c>
+      <c r="W23" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y23" s="14"/>
       <c r="Z23" s="13" t="s">
@@ -5564,18 +5661,23 @@
       <c r="J24" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="12"/>
+      <c r="K24" s="10">
+        <v>41</v>
+      </c>
+      <c r="L24" s="12">
+        <v>914286</v>
+      </c>
       <c r="M24" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N24" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O24" s="11" t="e">
+        <v>98000</v>
+      </c>
+      <c r="O24" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.12005596077845265</v>
       </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="13" t="s">
@@ -5584,15 +5686,15 @@
       <c r="T24" s="12"/>
       <c r="U24" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-41</v>
       </c>
       <c r="V24" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W24" s="11" t="e">
+        <v>-914286</v>
+      </c>
+      <c r="W24" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y24" s="14"/>
       <c r="Z24" s="13" t="s">
@@ -5780,18 +5882,23 @@
       <c r="J25" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="L25" s="12"/>
+      <c r="K25" s="10">
+        <v>196</v>
+      </c>
+      <c r="L25" s="12">
+        <v>8794667</v>
+      </c>
       <c r="M25" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="N25" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O25" s="11" t="e">
+        <v>1374381</v>
+      </c>
+      <c r="O25" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.18521941068039696</v>
       </c>
       <c r="Q25" s="14"/>
       <c r="R25" s="13" t="s">
@@ -5800,15 +5907,15 @@
       <c r="T25" s="12"/>
       <c r="U25" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-196</v>
       </c>
       <c r="V25" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W25" s="11" t="e">
+        <v>-8794667</v>
+      </c>
+      <c r="W25" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y25" s="14"/>
       <c r="Z25" s="13" t="s">
@@ -5997,19 +6104,23 @@
         <v>12</v>
       </c>
       <c r="J26" s="9"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="7"/>
+      <c r="K26" s="8">
+        <v>910</v>
+      </c>
+      <c r="L26" s="7">
+        <v>12507998</v>
+      </c>
       <c r="M26" s="27">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="N26" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O26" s="29" t="e">
+        <v>1622116</v>
+      </c>
+      <c r="O26" s="29">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.14901098505385232</v>
       </c>
       <c r="Q26" s="9" t="s">
         <v>12</v>
@@ -6019,15 +6130,15 @@
       <c r="T26" s="7"/>
       <c r="U26" s="27">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-910</v>
       </c>
       <c r="V26" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W26" s="29" t="e">
+        <v>-12507998</v>
+      </c>
+      <c r="W26" s="29">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y26" s="9" t="s">
         <v>12</v>
@@ -6227,10 +6338,13 @@
       <c r="J27" s="32" t="s">
         <v>19</v>
       </c>
+      <c r="K27" s="1">
+        <v>8499</v>
+      </c>
       <c r="L27" s="35"/>
       <c r="M27" s="10">
         <f t="shared" si="0"/>
-        <v>-9848</v>
+        <v>-1349</v>
       </c>
       <c r="N27" s="12">
         <f t="shared" si="0"/>
@@ -6249,7 +6363,7 @@
       <c r="T27" s="35"/>
       <c r="U27" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-8499</v>
       </c>
       <c r="V27" s="12">
         <f t="shared" si="3"/>
@@ -6468,10 +6582,13 @@
       <c r="J28" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="K28" s="1">
+        <v>3</v>
+      </c>
       <c r="L28" s="35"/>
       <c r="M28" s="10">
         <f t="shared" si="0"/>
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="N28" s="12">
         <f t="shared" si="0"/>
@@ -6488,7 +6605,7 @@
       <c r="T28" s="35"/>
       <c r="U28" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="V28" s="12">
         <f t="shared" si="3"/>
@@ -6688,18 +6805,23 @@
       <c r="J29" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="L29" s="12"/>
+      <c r="K29" s="10">
+        <v>136</v>
+      </c>
+      <c r="L29" s="12">
+        <v>146234</v>
+      </c>
       <c r="M29" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N29" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O29" s="11" t="e">
+        <v>5767</v>
+      </c>
+      <c r="O29" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>4.1055906369467564E-2</v>
       </c>
       <c r="Q29" s="14"/>
       <c r="R29" s="13" t="s">
@@ -6708,15 +6830,15 @@
       <c r="T29" s="12"/>
       <c r="U29" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-136</v>
       </c>
       <c r="V29" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W29" s="11" t="e">
+        <v>-146234</v>
+      </c>
+      <c r="W29" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y29" s="14"/>
       <c r="Z29" s="13" t="s">
@@ -6904,18 +7026,23 @@
       <c r="J30" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="L30" s="12"/>
+      <c r="K30" s="10">
+        <v>105</v>
+      </c>
+      <c r="L30" s="12">
+        <v>102525</v>
+      </c>
       <c r="M30" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O30" s="11" t="e">
+        <v>14818</v>
+      </c>
+      <c r="O30" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.16894888663390609</v>
       </c>
       <c r="Q30" s="14"/>
       <c r="R30" s="13" t="s">
@@ -6924,15 +7051,15 @@
       <c r="T30" s="12"/>
       <c r="U30" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-105</v>
       </c>
       <c r="V30" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W30" s="11" t="e">
+        <v>-102525</v>
+      </c>
+      <c r="W30" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y30" s="14"/>
       <c r="Z30" s="13" t="s">
@@ -7120,18 +7247,23 @@
       <c r="J31" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="L31" s="12"/>
+      <c r="K31" s="10">
+        <v>36</v>
+      </c>
+      <c r="L31" s="12">
+        <v>196133</v>
+      </c>
       <c r="M31" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="N31" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O31" s="11" t="e">
+        <v>-16267</v>
+      </c>
+      <c r="O31" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>-7.6586629001883233E-2</v>
       </c>
       <c r="Q31" s="14"/>
       <c r="R31" s="13" t="s">
@@ -7140,15 +7272,15 @@
       <c r="T31" s="12"/>
       <c r="U31" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-36</v>
       </c>
       <c r="V31" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W31" s="11" t="e">
+        <v>-196133</v>
+      </c>
+      <c r="W31" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y31" s="14"/>
       <c r="Z31" s="13" t="s">
@@ -7336,18 +7468,23 @@
       <c r="J32" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="L32" s="12"/>
+      <c r="K32" s="10">
+        <v>11</v>
+      </c>
+      <c r="L32" s="12">
+        <v>190857</v>
+      </c>
       <c r="M32" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-29</v>
       </c>
       <c r="N32" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O32" s="11" t="e">
+        <v>-397333</v>
+      </c>
+      <c r="O32" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>-0.67551811489484692</v>
       </c>
       <c r="Q32" s="14"/>
       <c r="R32" s="13" t="s">
@@ -7356,15 +7493,15 @@
       <c r="T32" s="12"/>
       <c r="U32" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="V32" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W32" s="11" t="e">
+        <v>-190857</v>
+      </c>
+      <c r="W32" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y32" s="14"/>
       <c r="Z32" s="13" t="s">
@@ -7552,18 +7689,23 @@
       <c r="J33" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="L33" s="12"/>
+      <c r="K33" s="10">
+        <v>3</v>
+      </c>
+      <c r="L33" s="12">
+        <v>7970</v>
+      </c>
       <c r="M33" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N33" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O33" s="11" t="e">
+        <v>-10</v>
+      </c>
+      <c r="O33" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>-1.2531328320802004E-3</v>
       </c>
       <c r="Q33" s="14"/>
       <c r="R33" s="13" t="s">
@@ -7572,15 +7714,15 @@
       <c r="T33" s="12"/>
       <c r="U33" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="V33" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W33" s="11" t="e">
+        <v>-7970</v>
+      </c>
+      <c r="W33" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y33" s="14"/>
       <c r="Z33" s="13" t="s">
@@ -7768,18 +7910,23 @@
       <c r="J34" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="L34" s="12"/>
+      <c r="K34" s="10">
+        <v>3</v>
+      </c>
+      <c r="L34" s="12">
+        <v>90848</v>
+      </c>
       <c r="M34" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N34" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O34" s="11" t="e">
+        <v>658</v>
+      </c>
+      <c r="O34" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>7.2957090586539524E-3</v>
       </c>
       <c r="Q34" s="14"/>
       <c r="R34" s="13" t="s">
@@ -7788,15 +7935,15 @@
       <c r="T34" s="12"/>
       <c r="U34" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="V34" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W34" s="11" t="e">
+        <v>-90848</v>
+      </c>
+      <c r="W34" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y34" s="14"/>
       <c r="Z34" s="13" t="s">
@@ -7984,18 +8131,23 @@
       <c r="J35" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="L35" s="12"/>
+      <c r="K35" s="10">
+        <v>12</v>
+      </c>
+      <c r="L35" s="12">
+        <v>275810</v>
+      </c>
       <c r="M35" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="N35" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O35" s="11" t="e">
+        <v>7334</v>
+      </c>
+      <c r="O35" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>2.7317153116107211E-2</v>
       </c>
       <c r="Q35" s="14"/>
       <c r="R35" s="13" t="s">
@@ -8004,15 +8156,15 @@
       <c r="T35" s="12"/>
       <c r="U35" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="V35" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W35" s="11" t="e">
+        <v>-275810</v>
+      </c>
+      <c r="W35" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y35" s="14"/>
       <c r="Z35" s="13" t="s">
@@ -8200,18 +8352,23 @@
       <c r="J36" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="L36" s="12"/>
+      <c r="K36" s="10">
+        <v>44</v>
+      </c>
+      <c r="L36" s="12">
+        <v>2032952</v>
+      </c>
       <c r="M36" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N36" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O36" s="11" t="e">
+        <v>1202608</v>
+      </c>
+      <c r="O36" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>1.4483250315531877</v>
       </c>
       <c r="Q36" s="14"/>
       <c r="R36" s="13" t="s">
@@ -8220,15 +8377,15 @@
       <c r="T36" s="12"/>
       <c r="U36" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-44</v>
       </c>
       <c r="V36" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W36" s="11" t="e">
+        <v>-2032952</v>
+      </c>
+      <c r="W36" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y36" s="14"/>
       <c r="Z36" s="13" t="s">
@@ -8417,19 +8574,23 @@
         <v>11</v>
       </c>
       <c r="J37" s="9"/>
-      <c r="K37" s="8"/>
-      <c r="L37" s="7"/>
+      <c r="K37" s="8">
+        <v>350</v>
+      </c>
+      <c r="L37" s="7">
+        <v>3043329</v>
+      </c>
       <c r="M37" s="27">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N37" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O37" s="29" t="e">
+        <v>817575</v>
+      </c>
+      <c r="O37" s="29">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.36732496044037211</v>
       </c>
       <c r="Q37" s="9" t="s">
         <v>11</v>
@@ -8439,15 +8600,15 @@
       <c r="T37" s="7"/>
       <c r="U37" s="27">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-350</v>
       </c>
       <c r="V37" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W37" s="29" t="e">
+        <v>-3043329</v>
+      </c>
+      <c r="W37" s="29">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y37" s="9" t="s">
         <v>11</v>
@@ -8647,10 +8808,13 @@
       <c r="J38" s="32" t="s">
         <v>19</v>
       </c>
+      <c r="K38" s="1">
+        <v>4044</v>
+      </c>
       <c r="L38" s="35"/>
       <c r="M38" s="10">
         <f t="shared" si="0"/>
-        <v>-4568</v>
+        <v>-524</v>
       </c>
       <c r="N38" s="12">
         <f t="shared" si="0"/>
@@ -8669,7 +8833,7 @@
       <c r="T38" s="35"/>
       <c r="U38" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-4044</v>
       </c>
       <c r="V38" s="12">
         <f t="shared" si="3"/>
@@ -8888,10 +9052,13 @@
       <c r="J39" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="K39" s="1">
+        <v>12</v>
+      </c>
       <c r="L39" s="35"/>
       <c r="M39" s="10">
         <f t="shared" si="0"/>
-        <v>-2</v>
+        <v>10</v>
       </c>
       <c r="N39" s="12">
         <f t="shared" si="0"/>
@@ -8908,7 +9075,7 @@
       <c r="T39" s="35"/>
       <c r="U39" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="V39" s="12">
         <f t="shared" si="3"/>
@@ -9107,18 +9274,23 @@
       <c r="J40" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="L40" s="12"/>
+      <c r="K40" s="10">
+        <v>194</v>
+      </c>
+      <c r="L40" s="12">
+        <v>189000</v>
+      </c>
       <c r="M40" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="N40" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O40" s="11" t="e">
+        <v>67602</v>
+      </c>
+      <c r="O40" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.55686255127761575</v>
       </c>
       <c r="Q40" s="14"/>
       <c r="R40" s="13" t="s">
@@ -9127,15 +9299,15 @@
       <c r="T40" s="12"/>
       <c r="U40" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-194</v>
       </c>
       <c r="V40" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W40" s="11" t="e">
+        <v>-189000</v>
+      </c>
+      <c r="W40" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y40" s="14"/>
       <c r="Z40" s="13" t="s">
@@ -9323,18 +9495,23 @@
       <c r="J41" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="L41" s="12"/>
+      <c r="K41" s="10">
+        <v>119</v>
+      </c>
+      <c r="L41" s="12">
+        <v>119887</v>
+      </c>
       <c r="M41" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="N41" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O41" s="11" t="e">
+        <v>51106</v>
+      </c>
+      <c r="O41" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.74302496328928047</v>
       </c>
       <c r="Q41" s="14"/>
       <c r="R41" s="13" t="s">
@@ -9343,15 +9520,15 @@
       <c r="T41" s="12"/>
       <c r="U41" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-119</v>
       </c>
       <c r="V41" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W41" s="11" t="e">
+        <v>-119887</v>
+      </c>
+      <c r="W41" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y41" s="14"/>
       <c r="Z41" s="13" t="s">
@@ -9539,18 +9716,23 @@
       <c r="J42" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="L42" s="12"/>
+      <c r="K42" s="10">
+        <v>19</v>
+      </c>
+      <c r="L42" s="12">
+        <v>108105</v>
+      </c>
       <c r="M42" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="N42" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O42" s="11" t="e">
+        <v>-26148</v>
+      </c>
+      <c r="O42" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>-0.19476659739447164</v>
       </c>
       <c r="Q42" s="14"/>
       <c r="R42" s="13" t="s">
@@ -9559,15 +9741,15 @@
       <c r="T42" s="12"/>
       <c r="U42" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="V42" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W42" s="11" t="e">
+        <v>-108105</v>
+      </c>
+      <c r="W42" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y42" s="14"/>
       <c r="Z42" s="13" t="s">
@@ -9755,18 +9937,23 @@
       <c r="J43" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="L43" s="12"/>
+      <c r="K43" s="10">
+        <v>20</v>
+      </c>
+      <c r="L43" s="12">
+        <v>286190</v>
+      </c>
       <c r="M43" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N43" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O43" s="11" t="e">
+        <v>-47620</v>
+      </c>
+      <c r="O43" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>-0.14265600191725833</v>
       </c>
       <c r="Q43" s="14"/>
       <c r="R43" s="13" t="s">
@@ -9775,15 +9962,15 @@
       <c r="T43" s="12"/>
       <c r="U43" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="V43" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W43" s="11" t="e">
+        <v>-286190</v>
+      </c>
+      <c r="W43" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y43" s="14"/>
       <c r="Z43" s="13" t="s">
@@ -9971,18 +10158,23 @@
       <c r="J44" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="12"/>
+      <c r="K44" s="10">
+        <v>6</v>
+      </c>
+      <c r="L44" s="12">
+        <v>41740</v>
+      </c>
       <c r="M44" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N44" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O44" s="11" t="e">
+        <v>28970</v>
+      </c>
+      <c r="O44" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>2.2685982772122162</v>
       </c>
       <c r="Q44" s="14"/>
       <c r="R44" s="13" t="s">
@@ -9991,15 +10183,15 @@
       <c r="T44" s="12"/>
       <c r="U44" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="V44" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W44" s="11" t="e">
+        <v>-41740</v>
+      </c>
+      <c r="W44" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y44" s="14"/>
       <c r="Z44" s="13" t="s">
@@ -10190,18 +10382,23 @@
       <c r="J45" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="L45" s="12"/>
+      <c r="K45" s="10">
+        <v>10</v>
+      </c>
+      <c r="L45" s="12">
+        <v>321607</v>
+      </c>
       <c r="M45" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N45" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O45" s="11" t="e">
+        <v>202378</v>
+      </c>
+      <c r="O45" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>1.6973890580311837</v>
       </c>
       <c r="Q45" s="14"/>
       <c r="R45" s="13" t="s">
@@ -10210,15 +10407,15 @@
       <c r="T45" s="12"/>
       <c r="U45" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="V45" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W45" s="11" t="e">
+        <v>-321607</v>
+      </c>
+      <c r="W45" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y45" s="14"/>
       <c r="Z45" s="13" t="s">
@@ -10409,18 +10606,23 @@
       <c r="J46" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="L46" s="12"/>
+      <c r="K46" s="10">
+        <v>12</v>
+      </c>
+      <c r="L46" s="12">
+        <v>242952</v>
+      </c>
       <c r="M46" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N46" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O46" s="11" t="e">
+        <v>141047</v>
+      </c>
+      <c r="O46" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>1.3841028408812128</v>
       </c>
       <c r="Q46" s="14"/>
       <c r="R46" s="13" t="s">
@@ -10429,15 +10631,15 @@
       <c r="T46" s="12"/>
       <c r="U46" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="V46" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W46" s="11" t="e">
+        <v>-242952</v>
+      </c>
+      <c r="W46" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y46" s="14"/>
       <c r="Z46" s="13" t="s">
@@ -10628,18 +10830,23 @@
       <c r="J47" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="L47" s="12"/>
+      <c r="K47" s="10">
+        <v>70</v>
+      </c>
+      <c r="L47" s="12">
+        <v>3181905</v>
+      </c>
       <c r="M47" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="N47" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O47" s="11" t="e">
+        <v>1964381</v>
+      </c>
+      <c r="O47" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>1.6134228154845407</v>
       </c>
       <c r="Q47" s="14"/>
       <c r="R47" s="13" t="s">
@@ -10648,15 +10855,15 @@
       <c r="T47" s="12"/>
       <c r="U47" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-70</v>
       </c>
       <c r="V47" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W47" s="11" t="e">
+        <v>-3181905</v>
+      </c>
+      <c r="W47" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y47" s="14"/>
       <c r="Z47" s="13" t="s">
@@ -10848,19 +11055,23 @@
         <v>10</v>
       </c>
       <c r="J48" s="9"/>
-      <c r="K48" s="8"/>
-      <c r="L48" s="7"/>
+      <c r="K48" s="8">
+        <v>450</v>
+      </c>
+      <c r="L48" s="7">
+        <v>4491386</v>
+      </c>
       <c r="M48" s="27">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="N48" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O48" s="29" t="e">
+        <v>2381716</v>
+      </c>
+      <c r="O48" s="29">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>1.1289519213905492</v>
       </c>
       <c r="Q48" s="9" t="s">
         <v>10</v>
@@ -10870,15 +11081,15 @@
       <c r="T48" s="7"/>
       <c r="U48" s="27">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-450</v>
       </c>
       <c r="V48" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W48" s="29" t="e">
+        <v>-4491386</v>
+      </c>
+      <c r="W48" s="29">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y48" s="9" t="s">
         <v>10</v>
@@ -11316,10 +11527,13 @@
       <c r="J50" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="K50" s="1">
+        <v>7</v>
+      </c>
       <c r="L50" s="35"/>
       <c r="M50" s="10">
         <f t="shared" si="0"/>
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="N50" s="12">
         <f t="shared" si="0"/>
@@ -11336,7 +11550,7 @@
       <c r="T50" s="35"/>
       <c r="U50" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="V50" s="12">
         <f t="shared" si="3"/>
@@ -11536,18 +11750,23 @@
       <c r="J51" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="L51" s="12"/>
+      <c r="K51" s="10">
+        <v>274</v>
+      </c>
+      <c r="L51" s="12">
+        <v>277390</v>
+      </c>
       <c r="M51" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="N51" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O51" s="11" t="e">
+        <v>42046</v>
+      </c>
+      <c r="O51" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.17865762458358828</v>
       </c>
       <c r="Q51" s="14"/>
       <c r="R51" s="13" t="s">
@@ -11556,15 +11775,15 @@
       <c r="T51" s="12"/>
       <c r="U51" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-274</v>
       </c>
       <c r="V51" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W51" s="11" t="e">
+        <v>-277390</v>
+      </c>
+      <c r="W51" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y51" s="14"/>
       <c r="Z51" s="13" t="s">
@@ -11752,18 +11971,23 @@
       <c r="J52" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="L52" s="12"/>
+      <c r="K52" s="10">
+        <v>115</v>
+      </c>
+      <c r="L52" s="12">
+        <v>131696</v>
+      </c>
       <c r="M52" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="N52" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O52" s="11" t="e">
+        <v>-3961</v>
+      </c>
+      <c r="O52" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>-2.919864068938573E-2</v>
       </c>
       <c r="Q52" s="14"/>
       <c r="R52" s="13" t="s">
@@ -11772,15 +11996,15 @@
       <c r="T52" s="12"/>
       <c r="U52" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-115</v>
       </c>
       <c r="V52" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W52" s="11" t="e">
+        <v>-131696</v>
+      </c>
+      <c r="W52" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y52" s="14"/>
       <c r="Z52" s="13" t="s">
@@ -11968,18 +12192,23 @@
       <c r="J53" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="L53" s="12"/>
+      <c r="K53" s="10">
+        <v>35</v>
+      </c>
+      <c r="L53" s="12">
+        <v>199350</v>
+      </c>
       <c r="M53" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N53" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O53" s="11" t="e">
+        <v>40406</v>
+      </c>
+      <c r="O53" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.25421532111938794</v>
       </c>
       <c r="Q53" s="14"/>
       <c r="R53" s="13" t="s">
@@ -11988,15 +12217,15 @@
       <c r="T53" s="12"/>
       <c r="U53" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-35</v>
       </c>
       <c r="V53" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W53" s="11" t="e">
+        <v>-199350</v>
+      </c>
+      <c r="W53" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y53" s="14"/>
       <c r="Z53" s="13" t="s">
@@ -12184,18 +12413,23 @@
       <c r="J54" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="L54" s="12"/>
+      <c r="K54" s="10">
+        <v>15</v>
+      </c>
+      <c r="L54" s="12">
+        <v>248571</v>
+      </c>
       <c r="M54" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="N54" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O54" s="11" t="e">
+        <v>-303429</v>
+      </c>
+      <c r="O54" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>-0.5496902173913043</v>
       </c>
       <c r="Q54" s="14"/>
       <c r="R54" s="13" t="s">
@@ -12204,15 +12438,15 @@
       <c r="T54" s="12"/>
       <c r="U54" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="V54" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W54" s="11" t="e">
+        <v>-248571</v>
+      </c>
+      <c r="W54" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y54" s="14"/>
       <c r="Z54" s="13" t="s">
@@ -12400,18 +12634,23 @@
       <c r="J55" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="L55" s="12"/>
+      <c r="K55" s="10">
+        <v>5</v>
+      </c>
+      <c r="L55" s="12">
+        <v>31750</v>
+      </c>
       <c r="M55" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="N55" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O55" s="11" t="e">
+        <v>-27520</v>
+      </c>
+      <c r="O55" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>-0.46431584275350091</v>
       </c>
       <c r="Q55" s="14"/>
       <c r="R55" s="13" t="s">
@@ -12420,15 +12659,15 @@
       <c r="T55" s="12"/>
       <c r="U55" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="V55" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W55" s="11" t="e">
+        <v>-31750</v>
+      </c>
+      <c r="W55" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y55" s="14"/>
       <c r="Z55" s="13" t="s">
@@ -12619,18 +12858,23 @@
       <c r="J56" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="L56" s="12"/>
+      <c r="K56" s="10">
+        <v>12</v>
+      </c>
+      <c r="L56" s="12">
+        <v>422033</v>
+      </c>
       <c r="M56" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N56" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O56" s="11" t="e">
+        <v>128876</v>
+      </c>
+      <c r="O56" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.43961426812254184</v>
       </c>
       <c r="Q56" s="14"/>
       <c r="R56" s="13" t="s">
@@ -12639,15 +12883,15 @@
       <c r="T56" s="12"/>
       <c r="U56" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="V56" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W56" s="11" t="e">
+        <v>-422033</v>
+      </c>
+      <c r="W56" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y56" s="14"/>
       <c r="Z56" s="13" t="s">
@@ -12838,18 +13082,23 @@
       <c r="J57" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="L57" s="12"/>
+      <c r="K57" s="10">
+        <v>33</v>
+      </c>
+      <c r="L57" s="12">
+        <v>891619</v>
+      </c>
       <c r="M57" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N57" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O57" s="11" t="e">
+        <v>271809</v>
+      </c>
+      <c r="O57" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.43853600296865169</v>
       </c>
       <c r="Q57" s="14"/>
       <c r="R57" s="13" t="s">
@@ -12858,15 +13107,15 @@
       <c r="T57" s="12"/>
       <c r="U57" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-33</v>
       </c>
       <c r="V57" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W57" s="11" t="e">
+        <v>-891619</v>
+      </c>
+      <c r="W57" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y57" s="14"/>
       <c r="Z57" s="13" t="s">
@@ -13057,18 +13306,23 @@
       <c r="J58" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="L58" s="12"/>
+      <c r="K58" s="10">
+        <v>81</v>
+      </c>
+      <c r="L58" s="12">
+        <v>3641810</v>
+      </c>
       <c r="M58" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N58" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O58" s="11" t="e">
+        <v>-181142</v>
+      </c>
+      <c r="O58" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>-4.7382755525049752E-2</v>
       </c>
       <c r="Q58" s="14"/>
       <c r="R58" s="13" t="s">
@@ -13077,15 +13331,15 @@
       <c r="T58" s="12"/>
       <c r="U58" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-81</v>
       </c>
       <c r="V58" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W58" s="11" t="e">
+        <v>-3641810</v>
+      </c>
+      <c r="W58" s="11">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y58" s="14"/>
       <c r="Z58" s="13" t="s">
@@ -13277,19 +13531,23 @@
         <v>1</v>
       </c>
       <c r="J59" s="9"/>
-      <c r="K59" s="8"/>
-      <c r="L59" s="7"/>
+      <c r="K59" s="8">
+        <v>570</v>
+      </c>
+      <c r="L59" s="7">
+        <v>5844219</v>
+      </c>
       <c r="M59" s="27">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="N59" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O59" s="29" t="e">
+        <v>-32915</v>
+      </c>
+      <c r="O59" s="29">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>-5.6005188923716901E-3</v>
       </c>
       <c r="Q59" s="9" t="s">
         <v>1</v>
@@ -13299,15 +13557,15 @@
       <c r="T59" s="7"/>
       <c r="U59" s="27">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-570</v>
       </c>
       <c r="V59" s="28">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W59" s="29" t="e">
+        <v>-5844219</v>
+      </c>
+      <c r="W59" s="29">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y59" s="9" t="s">
         <v>1</v>
@@ -13505,19 +13763,23 @@
         <v>0</v>
       </c>
       <c r="J60" s="4"/>
-      <c r="K60" s="3"/>
-      <c r="L60" s="2"/>
+      <c r="K60" s="3">
+        <v>4257</v>
+      </c>
+      <c r="L60" s="2">
+        <v>58608292</v>
+      </c>
       <c r="M60" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>419</v>
       </c>
       <c r="N60" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O60" s="30" t="e">
+        <v>3268962</v>
+      </c>
+      <c r="O60" s="30">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>5.9071224751004396E-2</v>
       </c>
       <c r="Q60" s="4" t="s">
         <v>0</v>
@@ -13527,15 +13789,15 @@
       <c r="T60" s="2"/>
       <c r="U60" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-4257</v>
       </c>
       <c r="V60" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W60" s="30" t="e">
+        <v>-58608292</v>
+      </c>
+      <c r="W60" s="30">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Y60" s="4" t="s">
         <v>0</v>

--- a/data/FY27Q1.xlsx
+++ b/data/FY27Q1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA5314C4-9DD8-404B-B559-055F868EE544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD09CF6-6274-814A-AD4E-C4C7A82E277F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16760" yWindow="680" windowWidth="18640" windowHeight="20260" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="1940" yWindow="1580" windowWidth="18640" windowHeight="20260" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="27Q1" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="34">
   <si>
     <t>總計</t>
   </si>
@@ -179,6 +179,12 @@
   <si>
     <t>10/04~10/10</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>27Q1W3</t>
+  </si>
+  <si>
+    <t>10/11~10/17</t>
   </si>
 </sst>
 </file>
@@ -989,7 +995,9 @@
       </c>
       <c r="J1" s="26"/>
       <c r="L1" s="25"/>
-      <c r="Q1" s="26"/>
+      <c r="Q1" s="26" t="s">
+        <v>32</v>
+      </c>
       <c r="R1" s="26"/>
       <c r="T1" s="25"/>
       <c r="Y1" s="26"/>
@@ -1033,7 +1041,9 @@
       <c r="K2" s="23"/>
       <c r="M2" s="23"/>
       <c r="O2" s="23"/>
-      <c r="Q2" s="23"/>
+      <c r="Q2" s="23" t="s">
+        <v>33</v>
+      </c>
       <c r="S2" s="23"/>
       <c r="U2" s="23"/>
       <c r="W2" s="23"/>
@@ -1135,16 +1145,16 @@
         <v>13</v>
       </c>
       <c r="Q4" s="19" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="R4" s="19" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="S4" s="18" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="T4" s="17" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="U4" s="16" t="s">
         <v>13</v>
@@ -1406,13 +1416,15 @@
         <v>75</v>
       </c>
       <c r="R5" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="S5" s="40"/>
+        <v>25</v>
+      </c>
+      <c r="S5" s="40">
+        <v>11939</v>
+      </c>
       <c r="T5" s="1"/>
       <c r="U5" s="10">
         <f t="shared" ref="U5:U60" si="2">S5-K5</f>
-        <v>-17034</v>
+        <v>-5095</v>
       </c>
       <c r="V5" s="12">
         <f t="shared" ref="V5:V60" si="3">T5-L5</f>
@@ -1433,7 +1445,7 @@
       <c r="AB5" s="1"/>
       <c r="AC5" s="10">
         <f t="shared" ref="AC5:AD60" si="5">AA5-S5</f>
-        <v>0</v>
+        <v>-11939</v>
       </c>
       <c r="AD5" s="12">
         <f t="shared" si="5"/>
@@ -1664,7 +1676,7 @@
       </c>
       <c r="Q6" s="14"/>
       <c r="R6" s="32" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="T6" s="33"/>
       <c r="U6" s="10">
@@ -1887,18 +1899,23 @@
       <c r="R7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="T7" s="12"/>
+      <c r="S7" s="10">
+        <v>384</v>
+      </c>
+      <c r="T7" s="12">
+        <v>454592</v>
+      </c>
       <c r="U7" s="10">
         <f t="shared" si="2"/>
-        <v>-500</v>
+        <v>-116</v>
       </c>
       <c r="V7" s="12">
         <f t="shared" si="3"/>
-        <v>-569204</v>
+        <v>-114612</v>
       </c>
       <c r="W7" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.20135487452653178</v>
       </c>
       <c r="Y7" s="14"/>
       <c r="Z7" s="13" t="s">
@@ -1907,15 +1924,15 @@
       <c r="AB7" s="12"/>
       <c r="AC7" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-384</v>
       </c>
       <c r="AD7" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE7" s="11" t="e">
+        <v>-454592</v>
+      </c>
+      <c r="AE7" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG7" s="14"/>
       <c r="AH7" s="13" t="s">
@@ -2108,18 +2125,23 @@
       <c r="R8" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="T8" s="12"/>
+      <c r="S8" s="10">
+        <v>305</v>
+      </c>
+      <c r="T8" s="12">
+        <v>375928</v>
+      </c>
       <c r="U8" s="10">
         <f t="shared" si="2"/>
-        <v>-430</v>
+        <v>-125</v>
       </c>
       <c r="V8" s="12">
         <f t="shared" si="3"/>
-        <v>-882812</v>
+        <v>-506884</v>
       </c>
       <c r="W8" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.57416981191918548</v>
       </c>
       <c r="Y8" s="14"/>
       <c r="Z8" s="13" t="s">
@@ -2128,15 +2150,15 @@
       <c r="AB8" s="12"/>
       <c r="AC8" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-305</v>
       </c>
       <c r="AD8" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE8" s="11" t="e">
+        <v>-375928</v>
+      </c>
+      <c r="AE8" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG8" s="14"/>
       <c r="AH8" s="13" t="s">
@@ -2329,18 +2351,23 @@
       <c r="R9" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="T9" s="12"/>
+      <c r="S9" s="10">
+        <v>116</v>
+      </c>
+      <c r="T9" s="12">
+        <v>733396</v>
+      </c>
       <c r="U9" s="10">
         <f t="shared" si="2"/>
-        <v>-161</v>
+        <v>-45</v>
       </c>
       <c r="V9" s="12">
         <f t="shared" si="3"/>
-        <v>-956562</v>
+        <v>-223166</v>
       </c>
       <c r="W9" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.2333000892780604</v>
       </c>
       <c r="Y9" s="14"/>
       <c r="Z9" s="13" t="s">
@@ -2349,15 +2376,15 @@
       <c r="AB9" s="12"/>
       <c r="AC9" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-116</v>
       </c>
       <c r="AD9" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE9" s="11" t="e">
+        <v>-733396</v>
+      </c>
+      <c r="AE9" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG9" s="14"/>
       <c r="AH9" s="13" t="s">
@@ -2550,18 +2577,23 @@
       <c r="R10" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="T10" s="12"/>
+      <c r="S10" s="10">
+        <v>82</v>
+      </c>
+      <c r="T10" s="12">
+        <v>1161714</v>
+      </c>
       <c r="U10" s="10">
         <f t="shared" si="2"/>
-        <v>-137</v>
+        <v>-55</v>
       </c>
       <c r="V10" s="12">
         <f t="shared" si="3"/>
-        <v>-2066476</v>
+        <v>-904762</v>
       </c>
       <c r="W10" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.43782845772222856</v>
       </c>
       <c r="Y10" s="14"/>
       <c r="Z10" s="13" t="s">
@@ -2570,15 +2602,15 @@
       <c r="AB10" s="12"/>
       <c r="AC10" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-82</v>
       </c>
       <c r="AD10" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE10" s="11" t="e">
+        <v>-1161714</v>
+      </c>
+      <c r="AE10" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG10" s="14"/>
       <c r="AH10" s="13" t="s">
@@ -2771,18 +2803,23 @@
       <c r="R11" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="T11" s="12"/>
+      <c r="S11" s="10">
+        <v>16</v>
+      </c>
+      <c r="T11" s="12">
+        <v>86940</v>
+      </c>
       <c r="U11" s="10">
         <f t="shared" si="2"/>
-        <v>-21</v>
+        <v>-5</v>
       </c>
       <c r="V11" s="12">
         <f t="shared" si="3"/>
-        <v>-124470</v>
+        <v>-37530</v>
       </c>
       <c r="W11" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.30151843817787416</v>
       </c>
       <c r="Y11" s="14"/>
       <c r="Z11" s="13" t="s">
@@ -2791,15 +2828,15 @@
       <c r="AB11" s="12"/>
       <c r="AC11" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="AD11" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE11" s="11" t="e">
+        <v>-86940</v>
+      </c>
+      <c r="AE11" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG11" s="14"/>
       <c r="AH11" s="13" t="s">
@@ -2992,18 +3029,23 @@
       <c r="R12" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="T12" s="12"/>
+      <c r="S12" s="10">
+        <v>41</v>
+      </c>
+      <c r="T12" s="12">
+        <v>1769548</v>
+      </c>
       <c r="U12" s="10">
         <f t="shared" si="2"/>
-        <v>-89</v>
+        <v>-48</v>
       </c>
       <c r="V12" s="12">
         <f t="shared" si="3"/>
-        <v>-3715738</v>
+        <v>-1946190</v>
       </c>
       <c r="W12" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.52376943691939526</v>
       </c>
       <c r="Y12" s="14"/>
       <c r="Z12" s="13" t="s">
@@ -3012,15 +3054,15 @@
       <c r="AB12" s="12"/>
       <c r="AC12" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-41</v>
       </c>
       <c r="AD12" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE12" s="11" t="e">
+        <v>-1769548</v>
+      </c>
+      <c r="AE12" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG12" s="14"/>
       <c r="AH12" s="13" t="s">
@@ -3213,18 +3255,23 @@
       <c r="R13" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="T13" s="12"/>
+      <c r="S13" s="10">
+        <v>92</v>
+      </c>
+      <c r="T13" s="12">
+        <v>2215767</v>
+      </c>
       <c r="U13" s="10">
         <f t="shared" si="2"/>
-        <v>-122</v>
+        <v>-30</v>
       </c>
       <c r="V13" s="12">
         <f t="shared" si="3"/>
-        <v>-2705048</v>
+        <v>-489281</v>
       </c>
       <c r="W13" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.18087701216392463</v>
       </c>
       <c r="Y13" s="14"/>
       <c r="Z13" s="13" t="s">
@@ -3233,15 +3280,15 @@
       <c r="AB13" s="12"/>
       <c r="AC13" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-92</v>
       </c>
       <c r="AD13" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE13" s="11" t="e">
+        <v>-2215767</v>
+      </c>
+      <c r="AE13" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG13" s="14"/>
       <c r="AH13" s="13" t="s">
@@ -3434,18 +3481,23 @@
       <c r="R14" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="T14" s="12"/>
+      <c r="S14" s="10">
+        <v>445</v>
+      </c>
+      <c r="T14" s="12">
+        <v>18568095</v>
+      </c>
       <c r="U14" s="10">
         <f t="shared" si="2"/>
-        <v>-517</v>
+        <v>-72</v>
       </c>
       <c r="V14" s="12">
         <f t="shared" si="3"/>
-        <v>-21701050</v>
+        <v>-3132955</v>
       </c>
       <c r="W14" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.14436882086350661</v>
       </c>
       <c r="Y14" s="14"/>
       <c r="Z14" s="13" t="s">
@@ -3454,15 +3506,15 @@
       <c r="AB14" s="12"/>
       <c r="AC14" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-445</v>
       </c>
       <c r="AD14" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE14" s="11" t="e">
+        <v>-18568095</v>
+      </c>
+      <c r="AE14" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG14" s="14"/>
       <c r="AH14" s="13" t="s">
@@ -3653,22 +3705,26 @@
         <v>-4.4377643221306454E-2</v>
       </c>
       <c r="Q15" s="9" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="R15" s="9"/>
-      <c r="S15" s="8"/>
-      <c r="T15" s="7"/>
+      <c r="S15" s="8">
+        <v>1481</v>
+      </c>
+      <c r="T15" s="7">
+        <v>25365980</v>
+      </c>
       <c r="U15" s="27">
         <f t="shared" si="2"/>
-        <v>-1977</v>
+        <v>-496</v>
       </c>
       <c r="V15" s="28">
         <f t="shared" si="3"/>
-        <v>-32721360</v>
+        <v>-7355380</v>
       </c>
       <c r="W15" s="29">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.22478833398122816</v>
       </c>
       <c r="Y15" s="9" t="s">
         <v>18</v>
@@ -3678,15 +3734,15 @@
       <c r="AB15" s="7"/>
       <c r="AC15" s="27">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-1481</v>
       </c>
       <c r="AD15" s="28">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE15" s="29" t="e">
+        <v>-25365980</v>
+      </c>
+      <c r="AE15" s="29">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG15" s="9" t="s">
         <v>18</v>
@@ -3888,12 +3944,15 @@
         <v>76</v>
       </c>
       <c r="R16" s="32" t="s">
-        <v>19</v>
+        <v>25</v>
+      </c>
+      <c r="S16" s="1">
+        <v>6936</v>
       </c>
       <c r="T16" s="35"/>
       <c r="U16" s="10">
         <f t="shared" si="2"/>
-        <v>-9228</v>
+        <v>-2292</v>
       </c>
       <c r="V16" s="12">
         <f t="shared" si="3"/>
@@ -3912,7 +3971,7 @@
       <c r="AB16" s="35"/>
       <c r="AC16" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-6936</v>
       </c>
       <c r="AD16" s="12">
         <f t="shared" si="5"/>
@@ -4130,7 +4189,7 @@
       </c>
       <c r="Q17" s="14"/>
       <c r="R17" s="32" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="T17" s="35"/>
       <c r="U17" s="10">
@@ -4357,18 +4416,23 @@
       <c r="R18" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="T18" s="12"/>
+      <c r="S18" s="10">
+        <v>198</v>
+      </c>
+      <c r="T18" s="12">
+        <v>192710</v>
+      </c>
       <c r="U18" s="10">
         <f t="shared" si="2"/>
-        <v>-214</v>
+        <v>-16</v>
       </c>
       <c r="V18" s="12">
         <f t="shared" si="3"/>
-        <v>-218415</v>
+        <v>-25705</v>
       </c>
       <c r="W18" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.11768880342467321</v>
       </c>
       <c r="Y18" s="14"/>
       <c r="Z18" s="13" t="s">
@@ -4377,15 +4441,15 @@
       <c r="AB18" s="12"/>
       <c r="AC18" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-198</v>
       </c>
       <c r="AD18" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE18" s="11" t="e">
+        <v>-192710</v>
+      </c>
+      <c r="AE18" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG18" s="14"/>
       <c r="AH18" s="13" t="s">
@@ -4578,18 +4642,23 @@
       <c r="R19" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="T19" s="12"/>
+      <c r="S19" s="10">
+        <v>153</v>
+      </c>
+      <c r="T19" s="12">
+        <v>170870</v>
+      </c>
       <c r="U19" s="10">
         <f t="shared" si="2"/>
-        <v>-273</v>
+        <v>-120</v>
       </c>
       <c r="V19" s="12">
         <f t="shared" si="3"/>
-        <v>-350306</v>
+        <v>-179436</v>
       </c>
       <c r="W19" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.51222645344356077</v>
       </c>
       <c r="Y19" s="14"/>
       <c r="Z19" s="13" t="s">
@@ -4598,15 +4667,15 @@
       <c r="AB19" s="12"/>
       <c r="AC19" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-153</v>
       </c>
       <c r="AD19" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE19" s="11" t="e">
+        <v>-170870</v>
+      </c>
+      <c r="AE19" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG19" s="14"/>
       <c r="AH19" s="13" t="s">
@@ -4799,18 +4868,23 @@
       <c r="R20" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="T20" s="12"/>
+      <c r="S20" s="10">
+        <v>56</v>
+      </c>
+      <c r="T20" s="12">
+        <v>328038</v>
+      </c>
       <c r="U20" s="10">
         <f t="shared" si="2"/>
-        <v>-92</v>
+        <v>-36</v>
       </c>
       <c r="V20" s="12">
         <f t="shared" si="3"/>
-        <v>-519863</v>
+        <v>-191825</v>
       </c>
       <c r="W20" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.36899144582322652</v>
       </c>
       <c r="Y20" s="14"/>
       <c r="Z20" s="13" t="s">
@@ -4819,15 +4893,15 @@
       <c r="AB20" s="12"/>
       <c r="AC20" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-56</v>
       </c>
       <c r="AD20" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE20" s="11" t="e">
+        <v>-328038</v>
+      </c>
+      <c r="AE20" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG20" s="14"/>
       <c r="AH20" s="13" t="s">
@@ -5020,18 +5094,23 @@
       <c r="R21" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="T21" s="12"/>
+      <c r="S21" s="10">
+        <v>35</v>
+      </c>
+      <c r="T21" s="12">
+        <v>497619</v>
+      </c>
       <c r="U21" s="10">
         <f t="shared" si="2"/>
-        <v>-63</v>
+        <v>-28</v>
       </c>
       <c r="V21" s="12">
         <f t="shared" si="3"/>
-        <v>-997333</v>
+        <v>-499714</v>
       </c>
       <c r="W21" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.5010503011531755</v>
       </c>
       <c r="Y21" s="14"/>
       <c r="Z21" s="13" t="s">
@@ -5040,15 +5119,15 @@
       <c r="AB21" s="12"/>
       <c r="AC21" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-35</v>
       </c>
       <c r="AD21" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE21" s="11" t="e">
+        <v>-497619</v>
+      </c>
+      <c r="AE21" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG21" s="14"/>
       <c r="AH21" s="13" t="s">
@@ -5241,18 +5320,23 @@
       <c r="R22" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="T22" s="12"/>
+      <c r="S22" s="10">
+        <v>16</v>
+      </c>
+      <c r="T22" s="12">
+        <v>91640</v>
+      </c>
       <c r="U22" s="10">
         <f t="shared" si="2"/>
-        <v>-12</v>
+        <v>4</v>
       </c>
       <c r="V22" s="12">
         <f t="shared" si="3"/>
-        <v>-80080</v>
+        <v>11560</v>
       </c>
       <c r="W22" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.14435564435564435</v>
       </c>
       <c r="Y22" s="14"/>
       <c r="Z22" s="13" t="s">
@@ -5261,15 +5345,15 @@
       <c r="AB22" s="12"/>
       <c r="AC22" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="AD22" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE22" s="11" t="e">
+        <v>-91640</v>
+      </c>
+      <c r="AE22" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG22" s="14"/>
       <c r="AH22" s="13" t="s">
@@ -5462,18 +5546,23 @@
       <c r="R23" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="T23" s="12"/>
+      <c r="S23" s="10">
+        <v>15</v>
+      </c>
+      <c r="T23" s="12">
+        <v>617324</v>
+      </c>
       <c r="U23" s="10">
         <f t="shared" si="2"/>
-        <v>-19</v>
+        <v>-4</v>
       </c>
       <c r="V23" s="12">
         <f t="shared" si="3"/>
-        <v>-633048</v>
+        <v>-15724</v>
       </c>
       <c r="W23" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-2.4838558845458797E-2</v>
       </c>
       <c r="Y23" s="14"/>
       <c r="Z23" s="13" t="s">
@@ -5482,15 +5571,15 @@
       <c r="AB23" s="12"/>
       <c r="AC23" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="AD23" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE23" s="11" t="e">
+        <v>-617324</v>
+      </c>
+      <c r="AE23" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG23" s="14"/>
       <c r="AH23" s="13" t="s">
@@ -5683,18 +5772,23 @@
       <c r="R24" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="T24" s="12"/>
+      <c r="S24" s="10">
+        <v>26</v>
+      </c>
+      <c r="T24" s="12">
+        <v>563619</v>
+      </c>
       <c r="U24" s="10">
         <f t="shared" si="2"/>
-        <v>-41</v>
+        <v>-15</v>
       </c>
       <c r="V24" s="12">
         <f t="shared" si="3"/>
-        <v>-914286</v>
+        <v>-350667</v>
       </c>
       <c r="W24" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.38354191139315269</v>
       </c>
       <c r="Y24" s="14"/>
       <c r="Z24" s="13" t="s">
@@ -5703,15 +5797,15 @@
       <c r="AB24" s="12"/>
       <c r="AC24" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-26</v>
       </c>
       <c r="AD24" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE24" s="11" t="e">
+        <v>-563619</v>
+      </c>
+      <c r="AE24" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG24" s="14"/>
       <c r="AH24" s="13" t="s">
@@ -5904,18 +5998,23 @@
       <c r="R25" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="T25" s="12"/>
+      <c r="S25" s="10">
+        <v>160</v>
+      </c>
+      <c r="T25" s="12">
+        <v>7439048</v>
+      </c>
       <c r="U25" s="10">
         <f t="shared" si="2"/>
-        <v>-196</v>
+        <v>-36</v>
       </c>
       <c r="V25" s="12">
         <f t="shared" si="3"/>
-        <v>-8794667</v>
+        <v>-1355619</v>
       </c>
       <c r="W25" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.15414102660168941</v>
       </c>
       <c r="Y25" s="14"/>
       <c r="Z25" s="13" t="s">
@@ -5924,15 +6023,15 @@
       <c r="AB25" s="12"/>
       <c r="AC25" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-160</v>
       </c>
       <c r="AD25" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE25" s="11" t="e">
+        <v>-7439048</v>
+      </c>
+      <c r="AE25" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG25" s="14"/>
       <c r="AH25" s="13" t="s">
@@ -6126,19 +6225,23 @@
         <v>12</v>
       </c>
       <c r="R26" s="9"/>
-      <c r="S26" s="8"/>
-      <c r="T26" s="7"/>
+      <c r="S26" s="8">
+        <v>659</v>
+      </c>
+      <c r="T26" s="7">
+        <v>9900868</v>
+      </c>
       <c r="U26" s="27">
         <f t="shared" si="2"/>
-        <v>-910</v>
+        <v>-251</v>
       </c>
       <c r="V26" s="28">
         <f t="shared" si="3"/>
-        <v>-12507998</v>
+        <v>-2607130</v>
       </c>
       <c r="W26" s="29">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.20843703364839042</v>
       </c>
       <c r="Y26" s="9" t="s">
         <v>12</v>
@@ -6148,15 +6251,15 @@
       <c r="AB26" s="7"/>
       <c r="AC26" s="27">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-659</v>
       </c>
       <c r="AD26" s="28">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE26" s="29" t="e">
+        <v>-9900868</v>
+      </c>
+      <c r="AE26" s="29">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG26" s="9" t="s">
         <v>12</v>
@@ -6358,12 +6461,15 @@
         <v>77</v>
       </c>
       <c r="R27" s="32" t="s">
-        <v>19</v>
+        <v>25</v>
+      </c>
+      <c r="S27" s="1">
+        <v>5245</v>
       </c>
       <c r="T27" s="35"/>
       <c r="U27" s="10">
         <f t="shared" si="2"/>
-        <v>-8499</v>
+        <v>-3254</v>
       </c>
       <c r="V27" s="12">
         <f t="shared" si="3"/>
@@ -6382,7 +6488,7 @@
       <c r="AB27" s="35"/>
       <c r="AC27" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-5245</v>
       </c>
       <c r="AD27" s="12">
         <f t="shared" si="5"/>
@@ -6600,7 +6706,7 @@
       </c>
       <c r="Q28" s="14"/>
       <c r="R28" s="32" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="T28" s="35"/>
       <c r="U28" s="10">
@@ -6827,18 +6933,23 @@
       <c r="R29" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="T29" s="12"/>
+      <c r="S29" s="10">
+        <v>91</v>
+      </c>
+      <c r="T29" s="12">
+        <v>107237</v>
+      </c>
       <c r="U29" s="10">
         <f t="shared" si="2"/>
-        <v>-136</v>
+        <v>-45</v>
       </c>
       <c r="V29" s="12">
         <f t="shared" si="3"/>
-        <v>-146234</v>
+        <v>-38997</v>
       </c>
       <c r="W29" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.26667532858295606</v>
       </c>
       <c r="Y29" s="14"/>
       <c r="Z29" s="13" t="s">
@@ -6847,15 +6958,15 @@
       <c r="AB29" s="12"/>
       <c r="AC29" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-91</v>
       </c>
       <c r="AD29" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE29" s="11" t="e">
+        <v>-107237</v>
+      </c>
+      <c r="AE29" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG29" s="14"/>
       <c r="AH29" s="13" t="s">
@@ -7048,18 +7159,23 @@
       <c r="R30" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="T30" s="12"/>
+      <c r="S30" s="10">
+        <v>66</v>
+      </c>
+      <c r="T30" s="12">
+        <v>60752</v>
+      </c>
       <c r="U30" s="10">
         <f t="shared" si="2"/>
-        <v>-105</v>
+        <v>-39</v>
       </c>
       <c r="V30" s="12">
         <f t="shared" si="3"/>
-        <v>-102525</v>
+        <v>-41773</v>
       </c>
       <c r="W30" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.40744208729578152</v>
       </c>
       <c r="Y30" s="14"/>
       <c r="Z30" s="13" t="s">
@@ -7068,15 +7184,15 @@
       <c r="AB30" s="12"/>
       <c r="AC30" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-66</v>
       </c>
       <c r="AD30" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE30" s="11" t="e">
+        <v>-60752</v>
+      </c>
+      <c r="AE30" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG30" s="14"/>
       <c r="AH30" s="13" t="s">
@@ -7269,18 +7385,23 @@
       <c r="R31" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="T31" s="12"/>
+      <c r="S31" s="10">
+        <v>22</v>
+      </c>
+      <c r="T31" s="12">
+        <v>135981</v>
+      </c>
       <c r="U31" s="10">
         <f t="shared" si="2"/>
-        <v>-36</v>
+        <v>-14</v>
       </c>
       <c r="V31" s="12">
         <f t="shared" si="3"/>
-        <v>-196133</v>
+        <v>-60152</v>
       </c>
       <c r="W31" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.3066898482152417</v>
       </c>
       <c r="Y31" s="14"/>
       <c r="Z31" s="13" t="s">
@@ -7289,15 +7410,15 @@
       <c r="AB31" s="12"/>
       <c r="AC31" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="AD31" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE31" s="11" t="e">
+        <v>-135981</v>
+      </c>
+      <c r="AE31" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG31" s="14"/>
       <c r="AH31" s="13" t="s">
@@ -7490,18 +7611,23 @@
       <c r="R32" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="T32" s="12"/>
+      <c r="S32" s="10">
+        <v>13</v>
+      </c>
+      <c r="T32" s="12">
+        <v>186952</v>
+      </c>
       <c r="U32" s="10">
         <f t="shared" si="2"/>
-        <v>-11</v>
+        <v>2</v>
       </c>
       <c r="V32" s="12">
         <f t="shared" si="3"/>
-        <v>-190857</v>
+        <v>-3905</v>
       </c>
       <c r="W32" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-2.0460344655946597E-2</v>
       </c>
       <c r="Y32" s="14"/>
       <c r="Z32" s="13" t="s">
@@ -7510,15 +7636,15 @@
       <c r="AB32" s="12"/>
       <c r="AC32" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="AD32" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE32" s="11" t="e">
+        <v>-186952</v>
+      </c>
+      <c r="AE32" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG32" s="14"/>
       <c r="AH32" s="13" t="s">
@@ -7711,7 +7837,12 @@
       <c r="R33" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="T33" s="12"/>
+      <c r="S33" s="10">
+        <v>0</v>
+      </c>
+      <c r="T33" s="12">
+        <v>0</v>
+      </c>
       <c r="U33" s="10">
         <f t="shared" si="2"/>
         <v>-3</v>
@@ -7932,18 +8063,23 @@
       <c r="R34" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="T34" s="12"/>
+      <c r="S34" s="10">
+        <v>1</v>
+      </c>
+      <c r="T34" s="12">
+        <v>24667</v>
+      </c>
       <c r="U34" s="10">
         <f t="shared" si="2"/>
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="V34" s="12">
         <f t="shared" si="3"/>
-        <v>-90848</v>
+        <v>-66181</v>
       </c>
       <c r="W34" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.7284805389221557</v>
       </c>
       <c r="Y34" s="14"/>
       <c r="Z34" s="13" t="s">
@@ -7952,15 +8088,15 @@
       <c r="AB34" s="12"/>
       <c r="AC34" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD34" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE34" s="11" t="e">
+        <v>-24667</v>
+      </c>
+      <c r="AE34" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG34" s="14"/>
       <c r="AH34" s="13" t="s">
@@ -8153,18 +8289,23 @@
       <c r="R35" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="T35" s="12"/>
+      <c r="S35" s="10">
+        <v>3</v>
+      </c>
+      <c r="T35" s="12">
+        <v>81238</v>
+      </c>
       <c r="U35" s="10">
         <f t="shared" si="2"/>
-        <v>-12</v>
+        <v>-9</v>
       </c>
       <c r="V35" s="12">
         <f t="shared" si="3"/>
-        <v>-275810</v>
+        <v>-194572</v>
       </c>
       <c r="W35" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.70545665494362064</v>
       </c>
       <c r="Y35" s="14"/>
       <c r="Z35" s="13" t="s">
@@ -8173,15 +8314,15 @@
       <c r="AB35" s="12"/>
       <c r="AC35" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AD35" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE35" s="11" t="e">
+        <v>-81238</v>
+      </c>
+      <c r="AE35" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG35" s="14"/>
       <c r="AH35" s="13" t="s">
@@ -8374,18 +8515,23 @@
       <c r="R36" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="T36" s="12"/>
+      <c r="S36" s="10">
+        <v>59</v>
+      </c>
+      <c r="T36" s="12">
+        <v>2762000</v>
+      </c>
       <c r="U36" s="10">
         <f t="shared" si="2"/>
-        <v>-44</v>
+        <v>15</v>
       </c>
       <c r="V36" s="12">
         <f t="shared" si="3"/>
-        <v>-2032952</v>
+        <v>729048</v>
       </c>
       <c r="W36" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.35861545181588156</v>
       </c>
       <c r="Y36" s="14"/>
       <c r="Z36" s="13" t="s">
@@ -8394,15 +8540,15 @@
       <c r="AB36" s="12"/>
       <c r="AC36" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-59</v>
       </c>
       <c r="AD36" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE36" s="11" t="e">
+        <v>-2762000</v>
+      </c>
+      <c r="AE36" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG36" s="14"/>
       <c r="AH36" s="13" t="s">
@@ -8596,19 +8742,23 @@
         <v>11</v>
       </c>
       <c r="R37" s="9"/>
-      <c r="S37" s="8"/>
-      <c r="T37" s="7"/>
+      <c r="S37" s="8">
+        <v>255</v>
+      </c>
+      <c r="T37" s="7">
+        <v>3358827</v>
+      </c>
       <c r="U37" s="27">
         <f t="shared" si="2"/>
-        <v>-350</v>
+        <v>-95</v>
       </c>
       <c r="V37" s="28">
         <f t="shared" si="3"/>
-        <v>-3043329</v>
+        <v>315498</v>
       </c>
       <c r="W37" s="29">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.10366871278129969</v>
       </c>
       <c r="Y37" s="9" t="s">
         <v>11</v>
@@ -8618,15 +8768,15 @@
       <c r="AB37" s="7"/>
       <c r="AC37" s="27">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-255</v>
       </c>
       <c r="AD37" s="28">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE37" s="29" t="e">
+        <v>-3358827</v>
+      </c>
+      <c r="AE37" s="29">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG37" s="9" t="s">
         <v>11</v>
@@ -8828,12 +8978,15 @@
         <v>81</v>
       </c>
       <c r="R38" s="32" t="s">
-        <v>19</v>
+        <v>25</v>
+      </c>
+      <c r="S38" s="1">
+        <v>2648</v>
       </c>
       <c r="T38" s="35"/>
       <c r="U38" s="10">
         <f t="shared" si="2"/>
-        <v>-4044</v>
+        <v>-1396</v>
       </c>
       <c r="V38" s="12">
         <f t="shared" si="3"/>
@@ -8852,7 +9005,7 @@
       <c r="AB38" s="35"/>
       <c r="AC38" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-2648</v>
       </c>
       <c r="AD38" s="12">
         <f t="shared" si="5"/>
@@ -9070,7 +9223,7 @@
       </c>
       <c r="Q39" s="14"/>
       <c r="R39" s="32" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="T39" s="35"/>
       <c r="U39" s="10">
@@ -9296,18 +9449,23 @@
       <c r="R40" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="T40" s="12"/>
+      <c r="S40" s="10">
+        <v>173</v>
+      </c>
+      <c r="T40" s="12">
+        <v>152649</v>
+      </c>
       <c r="U40" s="10">
         <f t="shared" si="2"/>
-        <v>-194</v>
+        <v>-21</v>
       </c>
       <c r="V40" s="12">
         <f t="shared" si="3"/>
-        <v>-189000</v>
+        <v>-36351</v>
       </c>
       <c r="W40" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.19233333333333333</v>
       </c>
       <c r="Y40" s="14"/>
       <c r="Z40" s="13" t="s">
@@ -9316,15 +9474,15 @@
       <c r="AB40" s="12"/>
       <c r="AC40" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-173</v>
       </c>
       <c r="AD40" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE40" s="11" t="e">
+        <v>-152649</v>
+      </c>
+      <c r="AE40" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG40" s="14"/>
       <c r="AH40" s="13" t="s">
@@ -9517,18 +9675,23 @@
       <c r="R41" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="T41" s="12"/>
+      <c r="S41" s="10">
+        <v>100</v>
+      </c>
+      <c r="T41" s="12">
+        <v>118630</v>
+      </c>
       <c r="U41" s="10">
         <f t="shared" si="2"/>
-        <v>-119</v>
+        <v>-19</v>
       </c>
       <c r="V41" s="12">
         <f t="shared" si="3"/>
-        <v>-119887</v>
+        <v>-1257</v>
       </c>
       <c r="W41" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-1.048487325564907E-2</v>
       </c>
       <c r="Y41" s="14"/>
       <c r="Z41" s="13" t="s">
@@ -9537,15 +9700,15 @@
       <c r="AB41" s="12"/>
       <c r="AC41" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD41" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE41" s="11" t="e">
+        <v>-118630</v>
+      </c>
+      <c r="AE41" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG41" s="14"/>
       <c r="AH41" s="13" t="s">
@@ -9738,18 +9901,23 @@
       <c r="R42" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="T42" s="12"/>
+      <c r="S42" s="10">
+        <v>26</v>
+      </c>
+      <c r="T42" s="12">
+        <v>139181</v>
+      </c>
       <c r="U42" s="10">
         <f t="shared" si="2"/>
-        <v>-19</v>
+        <v>7</v>
       </c>
       <c r="V42" s="12">
         <f t="shared" si="3"/>
-        <v>-108105</v>
+        <v>31076</v>
       </c>
       <c r="W42" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.28746126451135467</v>
       </c>
       <c r="Y42" s="14"/>
       <c r="Z42" s="13" t="s">
@@ -9758,15 +9926,15 @@
       <c r="AB42" s="12"/>
       <c r="AC42" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-26</v>
       </c>
       <c r="AD42" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE42" s="11" t="e">
+        <v>-139181</v>
+      </c>
+      <c r="AE42" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG42" s="14"/>
       <c r="AH42" s="13" t="s">
@@ -9959,18 +10127,23 @@
       <c r="R43" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="T43" s="12"/>
+      <c r="S43" s="10">
+        <v>17</v>
+      </c>
+      <c r="T43" s="12">
+        <v>203143</v>
+      </c>
       <c r="U43" s="10">
         <f t="shared" si="2"/>
-        <v>-20</v>
+        <v>-3</v>
       </c>
       <c r="V43" s="12">
         <f t="shared" si="3"/>
-        <v>-286190</v>
+        <v>-83047</v>
       </c>
       <c r="W43" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.29018134805548762</v>
       </c>
       <c r="Y43" s="14"/>
       <c r="Z43" s="13" t="s">
@@ -9979,15 +10152,15 @@
       <c r="AB43" s="12"/>
       <c r="AC43" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="AD43" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE43" s="11" t="e">
+        <v>-203143</v>
+      </c>
+      <c r="AE43" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG43" s="14"/>
       <c r="AH43" s="13" t="s">
@@ -10180,18 +10353,23 @@
       <c r="R44" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="T44" s="12"/>
+      <c r="S44" s="10">
+        <v>4</v>
+      </c>
+      <c r="T44" s="12">
+        <v>29360</v>
+      </c>
       <c r="U44" s="10">
         <f t="shared" si="2"/>
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="V44" s="12">
         <f t="shared" si="3"/>
-        <v>-41740</v>
+        <v>-12380</v>
       </c>
       <c r="W44" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.29659798754192623</v>
       </c>
       <c r="Y44" s="14"/>
       <c r="Z44" s="13" t="s">
@@ -10200,15 +10378,15 @@
       <c r="AB44" s="12"/>
       <c r="AC44" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AD44" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE44" s="11" t="e">
+        <v>-29360</v>
+      </c>
+      <c r="AE44" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG44" s="14"/>
       <c r="AH44" s="13" t="s">
@@ -10404,18 +10582,23 @@
       <c r="R45" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="T45" s="12"/>
+      <c r="S45" s="10">
+        <v>6</v>
+      </c>
+      <c r="T45" s="12">
+        <v>213899</v>
+      </c>
       <c r="U45" s="10">
         <f t="shared" si="2"/>
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="V45" s="12">
         <f t="shared" si="3"/>
-        <v>-321607</v>
+        <v>-107708</v>
       </c>
       <c r="W45" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.33490564571044784</v>
       </c>
       <c r="Y45" s="14"/>
       <c r="Z45" s="13" t="s">
@@ -10424,15 +10607,15 @@
       <c r="AB45" s="12"/>
       <c r="AC45" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AD45" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE45" s="11" t="e">
+        <v>-213899</v>
+      </c>
+      <c r="AE45" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG45" s="14"/>
       <c r="AH45" s="13" t="s">
@@ -10628,18 +10811,23 @@
       <c r="R46" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="T46" s="12"/>
+      <c r="S46" s="10">
+        <v>13</v>
+      </c>
+      <c r="T46" s="12">
+        <v>304952</v>
+      </c>
       <c r="U46" s="10">
         <f t="shared" si="2"/>
-        <v>-12</v>
+        <v>1</v>
       </c>
       <c r="V46" s="12">
         <f t="shared" si="3"/>
-        <v>-242952</v>
+        <v>62000</v>
       </c>
       <c r="W46" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.25519444170041816</v>
       </c>
       <c r="Y46" s="14"/>
       <c r="Z46" s="13" t="s">
@@ -10648,15 +10836,15 @@
       <c r="AB46" s="12"/>
       <c r="AC46" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="AD46" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE46" s="11" t="e">
+        <v>-304952</v>
+      </c>
+      <c r="AE46" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG46" s="14"/>
       <c r="AH46" s="13" t="s">
@@ -10852,18 +11040,23 @@
       <c r="R47" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="T47" s="12"/>
+      <c r="S47" s="10">
+        <v>64</v>
+      </c>
+      <c r="T47" s="12">
+        <v>3029143</v>
+      </c>
       <c r="U47" s="10">
         <f t="shared" si="2"/>
-        <v>-70</v>
+        <v>-6</v>
       </c>
       <c r="V47" s="12">
         <f t="shared" si="3"/>
-        <v>-3181905</v>
+        <v>-152762</v>
       </c>
       <c r="W47" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-4.8009604309368133E-2</v>
       </c>
       <c r="Y47" s="14"/>
       <c r="Z47" s="13" t="s">
@@ -10872,15 +11065,15 @@
       <c r="AB47" s="12"/>
       <c r="AC47" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-64</v>
       </c>
       <c r="AD47" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE47" s="11" t="e">
+        <v>-3029143</v>
+      </c>
+      <c r="AE47" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG47" s="14"/>
       <c r="AH47" s="13" t="s">
@@ -11077,19 +11270,23 @@
         <v>10</v>
       </c>
       <c r="R48" s="9"/>
-      <c r="S48" s="8"/>
-      <c r="T48" s="7"/>
+      <c r="S48" s="8">
+        <v>403</v>
+      </c>
+      <c r="T48" s="7">
+        <v>4190957</v>
+      </c>
       <c r="U48" s="27">
         <f t="shared" si="2"/>
-        <v>-450</v>
+        <v>-47</v>
       </c>
       <c r="V48" s="28">
         <f t="shared" si="3"/>
-        <v>-4491386</v>
+        <v>-300429</v>
       </c>
       <c r="W48" s="29">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-6.6890042405618216E-2</v>
       </c>
       <c r="Y48" s="9" t="s">
         <v>10</v>
@@ -11099,15 +11296,15 @@
       <c r="AB48" s="7"/>
       <c r="AC48" s="27">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-403</v>
       </c>
       <c r="AD48" s="28">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE48" s="29" t="e">
+        <v>-4190957</v>
+      </c>
+      <c r="AE48" s="29">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG48" s="9" t="s">
         <v>10</v>
@@ -11303,7 +11500,7 @@
         <v>84</v>
       </c>
       <c r="R49" s="32" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="T49" s="35"/>
       <c r="U49" s="10">
@@ -11545,7 +11742,7 @@
       </c>
       <c r="Q50" s="14"/>
       <c r="R50" s="32" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="T50" s="35"/>
       <c r="U50" s="10">
@@ -11772,18 +11969,23 @@
       <c r="R51" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="T51" s="12"/>
+      <c r="S51" s="10">
+        <v>198</v>
+      </c>
+      <c r="T51" s="12">
+        <v>181024</v>
+      </c>
       <c r="U51" s="10">
         <f t="shared" si="2"/>
-        <v>-274</v>
+        <v>-76</v>
       </c>
       <c r="V51" s="12">
         <f t="shared" si="3"/>
-        <v>-277390</v>
+        <v>-96366</v>
       </c>
       <c r="W51" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.34740257399329466</v>
       </c>
       <c r="Y51" s="14"/>
       <c r="Z51" s="13" t="s">
@@ -11792,15 +11994,15 @@
       <c r="AB51" s="12"/>
       <c r="AC51" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-198</v>
       </c>
       <c r="AD51" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE51" s="11" t="e">
+        <v>-181024</v>
+      </c>
+      <c r="AE51" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG51" s="14"/>
       <c r="AH51" s="13" t="s">
@@ -11993,18 +12195,23 @@
       <c r="R52" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="T52" s="12"/>
+      <c r="S52" s="10">
+        <v>76</v>
+      </c>
+      <c r="T52" s="12">
+        <v>79095</v>
+      </c>
       <c r="U52" s="10">
         <f t="shared" si="2"/>
-        <v>-115</v>
+        <v>-39</v>
       </c>
       <c r="V52" s="12">
         <f t="shared" si="3"/>
-        <v>-131696</v>
+        <v>-52601</v>
       </c>
       <c r="W52" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.39941228283319158</v>
       </c>
       <c r="Y52" s="14"/>
       <c r="Z52" s="13" t="s">
@@ -12013,15 +12220,15 @@
       <c r="AB52" s="12"/>
       <c r="AC52" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-76</v>
       </c>
       <c r="AD52" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE52" s="11" t="e">
+        <v>-79095</v>
+      </c>
+      <c r="AE52" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG52" s="14"/>
       <c r="AH52" s="13" t="s">
@@ -12214,18 +12421,23 @@
       <c r="R53" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="T53" s="12"/>
+      <c r="S53" s="10">
+        <v>19</v>
+      </c>
+      <c r="T53" s="12">
+        <v>99057</v>
+      </c>
       <c r="U53" s="10">
         <f t="shared" si="2"/>
-        <v>-35</v>
+        <v>-16</v>
       </c>
       <c r="V53" s="12">
         <f t="shared" si="3"/>
-        <v>-199350</v>
+        <v>-100293</v>
       </c>
       <c r="W53" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.50310007524454481</v>
       </c>
       <c r="Y53" s="14"/>
       <c r="Z53" s="13" t="s">
@@ -12234,15 +12446,15 @@
       <c r="AB53" s="12"/>
       <c r="AC53" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="AD53" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE53" s="11" t="e">
+        <v>-99057</v>
+      </c>
+      <c r="AE53" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG53" s="14"/>
       <c r="AH53" s="13" t="s">
@@ -12435,18 +12647,23 @@
       <c r="R54" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="T54" s="12"/>
+      <c r="S54" s="10">
+        <v>18</v>
+      </c>
+      <c r="T54" s="12">
+        <v>247810</v>
+      </c>
       <c r="U54" s="10">
         <f t="shared" si="2"/>
-        <v>-15</v>
+        <v>3</v>
       </c>
       <c r="V54" s="12">
         <f t="shared" si="3"/>
-        <v>-248571</v>
+        <v>-761</v>
       </c>
       <c r="W54" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-3.0614995313210311E-3</v>
       </c>
       <c r="Y54" s="14"/>
       <c r="Z54" s="13" t="s">
@@ -12455,15 +12672,15 @@
       <c r="AB54" s="12"/>
       <c r="AC54" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="AD54" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE54" s="11" t="e">
+        <v>-247810</v>
+      </c>
+      <c r="AE54" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG54" s="14"/>
       <c r="AH54" s="13" t="s">
@@ -12656,18 +12873,23 @@
       <c r="R55" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="T55" s="12"/>
+      <c r="S55" s="10">
+        <v>5</v>
+      </c>
+      <c r="T55" s="12">
+        <v>19650</v>
+      </c>
       <c r="U55" s="10">
         <f t="shared" si="2"/>
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="V55" s="12">
         <f t="shared" si="3"/>
-        <v>-31750</v>
+        <v>-12100</v>
       </c>
       <c r="W55" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.38110236220472443</v>
       </c>
       <c r="Y55" s="14"/>
       <c r="Z55" s="13" t="s">
@@ -12676,15 +12898,15 @@
       <c r="AB55" s="12"/>
       <c r="AC55" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AD55" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE55" s="11" t="e">
+        <v>-19650</v>
+      </c>
+      <c r="AE55" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG55" s="14"/>
       <c r="AH55" s="13" t="s">
@@ -12880,18 +13102,23 @@
       <c r="R56" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="T56" s="12"/>
+      <c r="S56" s="10">
+        <v>7</v>
+      </c>
+      <c r="T56" s="12">
+        <v>275524</v>
+      </c>
       <c r="U56" s="10">
         <f t="shared" si="2"/>
-        <v>-12</v>
+        <v>-5</v>
       </c>
       <c r="V56" s="12">
         <f t="shared" si="3"/>
-        <v>-422033</v>
+        <v>-146509</v>
       </c>
       <c r="W56" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.34715057827231521</v>
       </c>
       <c r="Y56" s="14"/>
       <c r="Z56" s="13" t="s">
@@ -12900,15 +13127,15 @@
       <c r="AB56" s="12"/>
       <c r="AC56" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="AD56" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE56" s="11" t="e">
+        <v>-275524</v>
+      </c>
+      <c r="AE56" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG56" s="14"/>
       <c r="AH56" s="13" t="s">
@@ -13104,18 +13331,23 @@
       <c r="R57" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="T57" s="12"/>
+      <c r="S57" s="10">
+        <v>26</v>
+      </c>
+      <c r="T57" s="12">
+        <v>608952</v>
+      </c>
       <c r="U57" s="10">
         <f t="shared" si="2"/>
-        <v>-33</v>
+        <v>-7</v>
       </c>
       <c r="V57" s="12">
         <f t="shared" si="3"/>
-        <v>-891619</v>
+        <v>-282667</v>
       </c>
       <c r="W57" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.31702666721996725</v>
       </c>
       <c r="Y57" s="14"/>
       <c r="Z57" s="13" t="s">
@@ -13124,15 +13356,15 @@
       <c r="AB57" s="12"/>
       <c r="AC57" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-26</v>
       </c>
       <c r="AD57" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE57" s="11" t="e">
+        <v>-608952</v>
+      </c>
+      <c r="AE57" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG57" s="14"/>
       <c r="AH57" s="13" t="s">
@@ -13328,18 +13560,23 @@
       <c r="R58" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="T58" s="12"/>
+      <c r="S58" s="10">
+        <v>112</v>
+      </c>
+      <c r="T58" s="12">
+        <v>4536000</v>
+      </c>
       <c r="U58" s="10">
         <f t="shared" si="2"/>
-        <v>-81</v>
+        <v>31</v>
       </c>
       <c r="V58" s="12">
         <f t="shared" si="3"/>
-        <v>-3641810</v>
+        <v>894190</v>
       </c>
       <c r="W58" s="11">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>0.2455345007015742</v>
       </c>
       <c r="Y58" s="14"/>
       <c r="Z58" s="13" t="s">
@@ -13348,15 +13585,15 @@
       <c r="AB58" s="12"/>
       <c r="AC58" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-112</v>
       </c>
       <c r="AD58" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE58" s="11" t="e">
+        <v>-4536000</v>
+      </c>
+      <c r="AE58" s="11">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG58" s="14"/>
       <c r="AH58" s="13" t="s">
@@ -13553,19 +13790,23 @@
         <v>1</v>
       </c>
       <c r="R59" s="9"/>
-      <c r="S59" s="8"/>
-      <c r="T59" s="7"/>
+      <c r="S59" s="8">
+        <v>461</v>
+      </c>
+      <c r="T59" s="7">
+        <v>6047112</v>
+      </c>
       <c r="U59" s="27">
         <f t="shared" si="2"/>
-        <v>-570</v>
+        <v>-109</v>
       </c>
       <c r="V59" s="28">
         <f t="shared" si="3"/>
-        <v>-5844219</v>
+        <v>202893</v>
       </c>
       <c r="W59" s="29">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>3.4716871493008734E-2</v>
       </c>
       <c r="Y59" s="9" t="s">
         <v>1</v>
@@ -13575,15 +13816,15 @@
       <c r="AB59" s="7"/>
       <c r="AC59" s="27">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-461</v>
       </c>
       <c r="AD59" s="28">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE59" s="29" t="e">
+        <v>-6047112</v>
+      </c>
+      <c r="AE59" s="29">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG59" s="9" t="s">
         <v>1</v>
@@ -13785,19 +14026,23 @@
         <v>0</v>
       </c>
       <c r="R60" s="4"/>
-      <c r="S60" s="3"/>
-      <c r="T60" s="2"/>
+      <c r="S60" s="3">
+        <v>3259</v>
+      </c>
+      <c r="T60" s="2">
+        <v>48863744</v>
+      </c>
       <c r="U60" s="6">
         <f t="shared" si="2"/>
-        <v>-4257</v>
+        <v>-998</v>
       </c>
       <c r="V60" s="5">
         <f t="shared" si="3"/>
-        <v>-58608292</v>
+        <v>-9744548</v>
       </c>
       <c r="W60" s="30">
         <f t="shared" si="4"/>
-        <v>-1</v>
+        <v>-0.1662656881384634</v>
       </c>
       <c r="Y60" s="4" t="s">
         <v>0</v>
@@ -13807,15 +14052,15 @@
       <c r="AB60" s="2"/>
       <c r="AC60" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-3259</v>
       </c>
       <c r="AD60" s="5">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE60" s="30" t="e">
+        <v>-48863744</v>
+      </c>
+      <c r="AE60" s="30">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AG60" s="4" t="s">
         <v>0</v>

--- a/data/FY27Q1.xlsx
+++ b/data/FY27Q1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD09CF6-6274-814A-AD4E-C4C7A82E277F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D1E1873-A8BA-654E-B27C-1ED94B48BDC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1940" yWindow="1580" windowWidth="18640" windowHeight="20260" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="15220" yWindow="1020" windowWidth="18640" windowHeight="20260" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="27Q1" sheetId="2" r:id="rId1"/>
@@ -1678,10 +1678,13 @@
       <c r="R6" s="32" t="s">
         <v>26</v>
       </c>
+      <c r="S6" s="15">
+        <v>48</v>
+      </c>
       <c r="T6" s="33"/>
       <c r="U6" s="10">
         <f t="shared" si="2"/>
-        <v>-22</v>
+        <v>26</v>
       </c>
       <c r="V6" s="12">
         <f t="shared" si="3"/>
@@ -1698,7 +1701,7 @@
       <c r="AB6" s="33"/>
       <c r="AC6" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-48</v>
       </c>
       <c r="AD6" s="12">
         <f t="shared" si="5"/>
@@ -4191,10 +4194,13 @@
       <c r="R17" s="32" t="s">
         <v>26</v>
       </c>
+      <c r="S17" s="1">
+        <v>26</v>
+      </c>
       <c r="T17" s="35"/>
       <c r="U17" s="10">
         <f t="shared" si="2"/>
-        <v>-26</v>
+        <v>0</v>
       </c>
       <c r="V17" s="12">
         <f t="shared" si="3"/>
@@ -4211,7 +4217,7 @@
       <c r="AB17" s="35"/>
       <c r="AC17" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-26</v>
       </c>
       <c r="AD17" s="12">
         <f t="shared" si="5"/>
@@ -6708,10 +6714,13 @@
       <c r="R28" s="32" t="s">
         <v>26</v>
       </c>
+      <c r="S28" s="1">
+        <v>6</v>
+      </c>
       <c r="T28" s="35"/>
       <c r="U28" s="10">
         <f t="shared" si="2"/>
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="V28" s="12">
         <f t="shared" si="3"/>
@@ -6728,7 +6737,7 @@
       <c r="AB28" s="35"/>
       <c r="AC28" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AD28" s="12">
         <f t="shared" si="5"/>
@@ -9225,10 +9234,13 @@
       <c r="R39" s="32" t="s">
         <v>26</v>
       </c>
+      <c r="S39" s="1">
+        <v>3</v>
+      </c>
       <c r="T39" s="35"/>
       <c r="U39" s="10">
         <f t="shared" si="2"/>
-        <v>-12</v>
+        <v>-9</v>
       </c>
       <c r="V39" s="12">
         <f t="shared" si="3"/>
@@ -9245,7 +9257,7 @@
       <c r="AB39" s="35"/>
       <c r="AC39" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AD39" s="12">
         <f t="shared" si="5"/>
@@ -11744,10 +11756,13 @@
       <c r="R50" s="32" t="s">
         <v>26</v>
       </c>
+      <c r="S50" s="1">
+        <v>6</v>
+      </c>
       <c r="T50" s="35"/>
       <c r="U50" s="10">
         <f t="shared" si="2"/>
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="V50" s="12">
         <f t="shared" si="3"/>
@@ -11764,7 +11779,7 @@
       <c r="AB50" s="35"/>
       <c r="AC50" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AD50" s="12">
         <f t="shared" si="5"/>

--- a/data/FY27Q1.xlsx
+++ b/data/FY27Q1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D1E1873-A8BA-654E-B27C-1ED94B48BDC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82DDDCB1-8A71-F449-8551-A6687578C1E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15220" yWindow="1020" windowWidth="18640" windowHeight="20260" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="15220" yWindow="780" windowWidth="18640" windowHeight="20260" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="27Q1" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="36">
   <si>
     <t>總計</t>
   </si>
@@ -185,6 +185,14 @@
   </si>
   <si>
     <t>10/11~10/17</t>
+  </si>
+  <si>
+    <t>27Q1W4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10/18~10/24</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -575,7 +583,12 @@
     <cellStyle name="一般 2" xfId="2" xr:uid="{0CB5398D-811F-454E-A670-53B654D1D081}"/>
     <cellStyle name="百分比" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1000,7 +1013,9 @@
       </c>
       <c r="R1" s="26"/>
       <c r="T1" s="25"/>
-      <c r="Y1" s="26"/>
+      <c r="Y1" s="26" t="s">
+        <v>34</v>
+      </c>
       <c r="Z1" s="26"/>
       <c r="AB1" s="25"/>
       <c r="AG1" s="26"/>
@@ -1047,7 +1062,9 @@
       <c r="S2" s="23"/>
       <c r="U2" s="23"/>
       <c r="W2" s="23"/>
-      <c r="Y2" s="23"/>
+      <c r="Y2" s="23" t="s">
+        <v>35</v>
+      </c>
       <c r="Z2" s="22"/>
       <c r="AB2" s="21"/>
       <c r="AG2" s="23"/>
@@ -1441,11 +1458,13 @@
       <c r="Z5" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="AA5" s="40"/>
+      <c r="AA5" s="40">
+        <v>9977</v>
+      </c>
       <c r="AB5" s="1"/>
       <c r="AC5" s="10">
         <f t="shared" ref="AC5:AD60" si="5">AA5-S5</f>
-        <v>-11939</v>
+        <v>-1962</v>
       </c>
       <c r="AD5" s="12">
         <f t="shared" si="5"/>
@@ -1466,7 +1485,7 @@
       <c r="AJ5" s="43"/>
       <c r="AK5" s="10">
         <f t="shared" ref="AK5:AL60" si="7">AI5-AA5</f>
-        <v>0</v>
+        <v>-9977</v>
       </c>
       <c r="AL5" s="12">
         <f t="shared" si="7"/>
@@ -1924,18 +1943,23 @@
       <c r="Z7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AB7" s="12"/>
+      <c r="AA7" s="10">
+        <v>253</v>
+      </c>
+      <c r="AB7" s="12">
+        <v>259752</v>
+      </c>
       <c r="AC7" s="10">
         <f t="shared" si="5"/>
-        <v>-384</v>
+        <v>-131</v>
       </c>
       <c r="AD7" s="12">
         <f t="shared" si="5"/>
-        <v>-454592</v>
+        <v>-194840</v>
       </c>
       <c r="AE7" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.42860411093903983</v>
       </c>
       <c r="AG7" s="14"/>
       <c r="AH7" s="13" t="s">
@@ -1945,15 +1969,15 @@
       <c r="AJ7" s="45"/>
       <c r="AK7" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-253</v>
       </c>
       <c r="AL7" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM7" s="11" t="e">
+        <v>-259752</v>
+      </c>
+      <c r="AM7" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO7" s="14"/>
       <c r="AP7" s="13" t="s">
@@ -2150,18 +2174,23 @@
       <c r="Z8" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AB8" s="12"/>
+      <c r="AA8" s="10">
+        <v>289</v>
+      </c>
+      <c r="AB8" s="12">
+        <v>465571</v>
+      </c>
       <c r="AC8" s="10">
         <f t="shared" si="5"/>
-        <v>-305</v>
+        <v>-16</v>
       </c>
       <c r="AD8" s="12">
         <f t="shared" si="5"/>
-        <v>-375928</v>
+        <v>89643</v>
       </c>
       <c r="AE8" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>0.23845789619288801</v>
       </c>
       <c r="AG8" s="14"/>
       <c r="AH8" s="13" t="s">
@@ -2171,15 +2200,15 @@
       <c r="AJ8" s="45"/>
       <c r="AK8" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-289</v>
       </c>
       <c r="AL8" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM8" s="11" t="e">
+        <v>-465571</v>
+      </c>
+      <c r="AM8" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO8" s="14"/>
       <c r="AP8" s="13" t="s">
@@ -2376,18 +2405,23 @@
       <c r="Z9" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AB9" s="12"/>
+      <c r="AA9" s="10">
+        <v>85</v>
+      </c>
+      <c r="AB9" s="12">
+        <v>494333</v>
+      </c>
       <c r="AC9" s="10">
         <f t="shared" si="5"/>
-        <v>-116</v>
+        <v>-31</v>
       </c>
       <c r="AD9" s="12">
         <f t="shared" si="5"/>
-        <v>-733396</v>
+        <v>-239063</v>
       </c>
       <c r="AE9" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.32596714462582288</v>
       </c>
       <c r="AG9" s="14"/>
       <c r="AH9" s="13" t="s">
@@ -2397,15 +2431,15 @@
       <c r="AJ9" s="45"/>
       <c r="AK9" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-85</v>
       </c>
       <c r="AL9" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM9" s="11" t="e">
+        <v>-494333</v>
+      </c>
+      <c r="AM9" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO9" s="14"/>
       <c r="AP9" s="13" t="s">
@@ -2602,18 +2636,23 @@
       <c r="Z10" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AB10" s="12"/>
+      <c r="AA10" s="10">
+        <v>44</v>
+      </c>
+      <c r="AB10" s="12">
+        <v>653719</v>
+      </c>
       <c r="AC10" s="10">
         <f t="shared" si="5"/>
-        <v>-82</v>
+        <v>-38</v>
       </c>
       <c r="AD10" s="12">
         <f t="shared" si="5"/>
-        <v>-1161714</v>
+        <v>-507995</v>
       </c>
       <c r="AE10" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.43728060434840244</v>
       </c>
       <c r="AG10" s="14"/>
       <c r="AH10" s="13" t="s">
@@ -2623,15 +2662,15 @@
       <c r="AJ10" s="45"/>
       <c r="AK10" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-44</v>
       </c>
       <c r="AL10" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM10" s="11" t="e">
+        <v>-653719</v>
+      </c>
+      <c r="AM10" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO10" s="14"/>
       <c r="AP10" s="13" t="s">
@@ -2828,18 +2867,23 @@
       <c r="Z11" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AB11" s="12"/>
+      <c r="AA11" s="10">
+        <v>26</v>
+      </c>
+      <c r="AB11" s="12">
+        <v>221740</v>
+      </c>
       <c r="AC11" s="10">
         <f t="shared" si="5"/>
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="AD11" s="12">
         <f t="shared" si="5"/>
-        <v>-86940</v>
+        <v>134800</v>
       </c>
       <c r="AE11" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>1.5504945939728549</v>
       </c>
       <c r="AG11" s="14"/>
       <c r="AH11" s="13" t="s">
@@ -2849,15 +2893,15 @@
       <c r="AJ11" s="45"/>
       <c r="AK11" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-26</v>
       </c>
       <c r="AL11" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM11" s="11" t="e">
+        <v>-221740</v>
+      </c>
+      <c r="AM11" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO11" s="14"/>
       <c r="AP11" s="13" t="s">
@@ -3054,18 +3098,23 @@
       <c r="Z12" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AB12" s="12"/>
+      <c r="AA12" s="10">
+        <v>35</v>
+      </c>
+      <c r="AB12" s="12">
+        <v>1283186</v>
+      </c>
       <c r="AC12" s="10">
         <f t="shared" si="5"/>
-        <v>-41</v>
+        <v>-6</v>
       </c>
       <c r="AD12" s="12">
         <f t="shared" si="5"/>
-        <v>-1769548</v>
+        <v>-486362</v>
       </c>
       <c r="AE12" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.27485097889404525</v>
       </c>
       <c r="AG12" s="14"/>
       <c r="AH12" s="13" t="s">
@@ -3075,15 +3124,15 @@
       <c r="AJ12" s="45"/>
       <c r="AK12" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-35</v>
       </c>
       <c r="AL12" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM12" s="11" t="e">
+        <v>-1283186</v>
+      </c>
+      <c r="AM12" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO12" s="14"/>
       <c r="AP12" s="13" t="s">
@@ -3280,18 +3329,23 @@
       <c r="Z13" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AB13" s="12"/>
+      <c r="AA13" s="10">
+        <v>61</v>
+      </c>
+      <c r="AB13" s="12">
+        <v>1367524</v>
+      </c>
       <c r="AC13" s="10">
         <f t="shared" si="5"/>
-        <v>-92</v>
+        <v>-31</v>
       </c>
       <c r="AD13" s="12">
         <f t="shared" si="5"/>
-        <v>-2215767</v>
+        <v>-848243</v>
       </c>
       <c r="AE13" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.38282138871099713</v>
       </c>
       <c r="AG13" s="14"/>
       <c r="AH13" s="13" t="s">
@@ -3301,15 +3355,15 @@
       <c r="AJ13" s="45"/>
       <c r="AK13" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-61</v>
       </c>
       <c r="AL13" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM13" s="11" t="e">
+        <v>-1367524</v>
+      </c>
+      <c r="AM13" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO13" s="14"/>
       <c r="AP13" s="13" t="s">
@@ -3506,18 +3560,23 @@
       <c r="Z14" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AB14" s="12"/>
+      <c r="AA14" s="10">
+        <v>232</v>
+      </c>
+      <c r="AB14" s="12">
+        <v>11920762</v>
+      </c>
       <c r="AC14" s="10">
         <f t="shared" si="5"/>
-        <v>-445</v>
+        <v>-213</v>
       </c>
       <c r="AD14" s="12">
         <f t="shared" si="5"/>
-        <v>-18568095</v>
+        <v>-6647333</v>
       </c>
       <c r="AE14" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.35799757594949833</v>
       </c>
       <c r="AG14" s="14"/>
       <c r="AH14" s="13" t="s">
@@ -3527,15 +3586,15 @@
       <c r="AJ14" s="45"/>
       <c r="AK14" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-232</v>
       </c>
       <c r="AL14" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM14" s="11" t="e">
+        <v>-11920762</v>
+      </c>
+      <c r="AM14" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO14" s="14"/>
       <c r="AP14" s="13" t="s">
@@ -3733,19 +3792,23 @@
         <v>18</v>
       </c>
       <c r="Z15" s="9"/>
-      <c r="AA15" s="8"/>
-      <c r="AB15" s="7"/>
+      <c r="AA15" s="8">
+        <v>1025</v>
+      </c>
+      <c r="AB15" s="7">
+        <v>16666587</v>
+      </c>
       <c r="AC15" s="27">
         <f t="shared" si="5"/>
-        <v>-1481</v>
+        <v>-456</v>
       </c>
       <c r="AD15" s="28">
         <f t="shared" si="5"/>
-        <v>-25365980</v>
+        <v>-8699393</v>
       </c>
       <c r="AE15" s="29">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.34295513124271171</v>
       </c>
       <c r="AG15" s="9" t="s">
         <v>18</v>
@@ -3755,15 +3818,15 @@
       <c r="AJ15" s="46"/>
       <c r="AK15" s="27">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-1025</v>
       </c>
       <c r="AL15" s="28">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM15" s="29" t="e">
+        <v>-16666587</v>
+      </c>
+      <c r="AM15" s="29">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO15" s="9" t="s">
         <v>27</v>
@@ -3971,10 +4034,13 @@
       <c r="Z16" s="32" t="s">
         <v>19</v>
       </c>
+      <c r="AA16" s="1">
+        <v>6445</v>
+      </c>
       <c r="AB16" s="35"/>
       <c r="AC16" s="10">
         <f t="shared" si="5"/>
-        <v>-6936</v>
+        <v>-491</v>
       </c>
       <c r="AD16" s="12">
         <f t="shared" si="5"/>
@@ -3994,7 +4060,7 @@
       <c r="AJ16" s="47"/>
       <c r="AK16" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-6445</v>
       </c>
       <c r="AL16" s="12">
         <f t="shared" si="7"/>
@@ -4444,18 +4510,23 @@
       <c r="Z18" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AB18" s="12"/>
+      <c r="AA18" s="10">
+        <v>188</v>
+      </c>
+      <c r="AB18" s="12">
+        <v>184788</v>
+      </c>
       <c r="AC18" s="10">
         <f t="shared" si="5"/>
-        <v>-198</v>
+        <v>-10</v>
       </c>
       <c r="AD18" s="12">
         <f t="shared" si="5"/>
-        <v>-192710</v>
+        <v>-7922</v>
       </c>
       <c r="AE18" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-4.1108401224638054E-2</v>
       </c>
       <c r="AG18" s="14"/>
       <c r="AH18" s="13" t="s">
@@ -4465,15 +4536,15 @@
       <c r="AJ18" s="45"/>
       <c r="AK18" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-188</v>
       </c>
       <c r="AL18" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM18" s="11" t="e">
+        <v>-184788</v>
+      </c>
+      <c r="AM18" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO18" s="14"/>
       <c r="AP18" s="13" t="s">
@@ -4670,18 +4741,23 @@
       <c r="Z19" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AB19" s="12"/>
+      <c r="AA19" s="10">
+        <v>144</v>
+      </c>
+      <c r="AB19" s="12">
+        <v>160800</v>
+      </c>
       <c r="AC19" s="10">
         <f t="shared" si="5"/>
-        <v>-153</v>
+        <v>-9</v>
       </c>
       <c r="AD19" s="12">
         <f t="shared" si="5"/>
-        <v>-170870</v>
+        <v>-10070</v>
       </c>
       <c r="AE19" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-5.8933692280681217E-2</v>
       </c>
       <c r="AG19" s="14"/>
       <c r="AH19" s="13" t="s">
@@ -4691,15 +4767,15 @@
       <c r="AJ19" s="45"/>
       <c r="AK19" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-144</v>
       </c>
       <c r="AL19" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM19" s="11" t="e">
+        <v>-160800</v>
+      </c>
+      <c r="AM19" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO19" s="14"/>
       <c r="AP19" s="13" t="s">
@@ -4896,18 +4972,23 @@
       <c r="Z20" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AB20" s="12"/>
+      <c r="AA20" s="10">
+        <v>40</v>
+      </c>
+      <c r="AB20" s="12">
+        <v>229238</v>
+      </c>
       <c r="AC20" s="10">
         <f t="shared" si="5"/>
-        <v>-56</v>
+        <v>-16</v>
       </c>
       <c r="AD20" s="12">
         <f t="shared" si="5"/>
-        <v>-328038</v>
+        <v>-98800</v>
       </c>
       <c r="AE20" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.30118461885513265</v>
       </c>
       <c r="AG20" s="14"/>
       <c r="AH20" s="13" t="s">
@@ -4917,15 +4998,15 @@
       <c r="AJ20" s="45"/>
       <c r="AK20" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="AL20" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM20" s="11" t="e">
+        <v>-229238</v>
+      </c>
+      <c r="AM20" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO20" s="14"/>
       <c r="AP20" s="13" t="s">
@@ -5122,18 +5203,23 @@
       <c r="Z21" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AB21" s="12"/>
+      <c r="AA21" s="10">
+        <v>24</v>
+      </c>
+      <c r="AB21" s="12">
+        <v>360095</v>
+      </c>
       <c r="AC21" s="10">
         <f t="shared" si="5"/>
-        <v>-35</v>
+        <v>-11</v>
       </c>
       <c r="AD21" s="12">
         <f t="shared" si="5"/>
-        <v>-497619</v>
+        <v>-137524</v>
       </c>
       <c r="AE21" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.27636404558507616</v>
       </c>
       <c r="AG21" s="14"/>
       <c r="AH21" s="13" t="s">
@@ -5143,15 +5229,15 @@
       <c r="AJ21" s="45"/>
       <c r="AK21" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="AL21" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM21" s="11" t="e">
+        <v>-360095</v>
+      </c>
+      <c r="AM21" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO21" s="14"/>
       <c r="AP21" s="13" t="s">
@@ -5348,18 +5434,23 @@
       <c r="Z22" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AB22" s="12"/>
+      <c r="AA22" s="10">
+        <v>14</v>
+      </c>
+      <c r="AB22" s="12">
+        <v>102560</v>
+      </c>
       <c r="AC22" s="10">
         <f t="shared" si="5"/>
-        <v>-16</v>
+        <v>-2</v>
       </c>
       <c r="AD22" s="12">
         <f t="shared" si="5"/>
-        <v>-91640</v>
+        <v>10920</v>
       </c>
       <c r="AE22" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>0.11916193801833261</v>
       </c>
       <c r="AG22" s="14"/>
       <c r="AH22" s="13" t="s">
@@ -5369,15 +5460,15 @@
       <c r="AJ22" s="45"/>
       <c r="AK22" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="AL22" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM22" s="11" t="e">
+        <v>-102560</v>
+      </c>
+      <c r="AM22" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO22" s="14"/>
       <c r="AP22" s="13" t="s">
@@ -5574,18 +5665,23 @@
       <c r="Z23" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AB23" s="12"/>
+      <c r="AA23" s="10">
+        <v>12</v>
+      </c>
+      <c r="AB23" s="12">
+        <v>430029</v>
+      </c>
       <c r="AC23" s="10">
         <f t="shared" si="5"/>
-        <v>-15</v>
+        <v>-3</v>
       </c>
       <c r="AD23" s="12">
         <f t="shared" si="5"/>
-        <v>-617324</v>
+        <v>-187295</v>
       </c>
       <c r="AE23" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.30339821552377683</v>
       </c>
       <c r="AG23" s="14"/>
       <c r="AH23" s="13" t="s">
@@ -5595,15 +5691,15 @@
       <c r="AJ23" s="45"/>
       <c r="AK23" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="AL23" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM23" s="11" t="e">
+        <v>-430029</v>
+      </c>
+      <c r="AM23" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO23" s="14"/>
       <c r="AP23" s="13" t="s">
@@ -5800,18 +5896,23 @@
       <c r="Z24" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AB24" s="12"/>
+      <c r="AA24" s="10">
+        <v>23</v>
+      </c>
+      <c r="AB24" s="12">
+        <v>479333</v>
+      </c>
       <c r="AC24" s="10">
         <f t="shared" si="5"/>
-        <v>-26</v>
+        <v>-3</v>
       </c>
       <c r="AD24" s="12">
         <f t="shared" si="5"/>
-        <v>-563619</v>
+        <v>-84286</v>
       </c>
       <c r="AE24" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.14954428434811459</v>
       </c>
       <c r="AG24" s="14"/>
       <c r="AH24" s="13" t="s">
@@ -5821,15 +5922,15 @@
       <c r="AJ24" s="45"/>
       <c r="AK24" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-23</v>
       </c>
       <c r="AL24" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM24" s="11" t="e">
+        <v>-479333</v>
+      </c>
+      <c r="AM24" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO24" s="14"/>
       <c r="AP24" s="13" t="s">
@@ -6026,18 +6127,23 @@
       <c r="Z25" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AB25" s="12"/>
+      <c r="AA25" s="10">
+        <v>109</v>
+      </c>
+      <c r="AB25" s="12">
+        <v>5364857</v>
+      </c>
       <c r="AC25" s="10">
         <f t="shared" si="5"/>
-        <v>-160</v>
+        <v>-51</v>
       </c>
       <c r="AD25" s="12">
         <f t="shared" si="5"/>
-        <v>-7439048</v>
+        <v>-2074191</v>
       </c>
       <c r="AE25" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.27882479048394365</v>
       </c>
       <c r="AG25" s="14"/>
       <c r="AH25" s="13" t="s">
@@ -6047,15 +6153,15 @@
       <c r="AJ25" s="45"/>
       <c r="AK25" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-109</v>
       </c>
       <c r="AL25" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM25" s="11" t="e">
+        <v>-5364857</v>
+      </c>
+      <c r="AM25" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO25" s="14"/>
       <c r="AP25" s="13" t="s">
@@ -6253,19 +6359,23 @@
         <v>12</v>
       </c>
       <c r="Z26" s="9"/>
-      <c r="AA26" s="8"/>
-      <c r="AB26" s="7"/>
+      <c r="AA26" s="8">
+        <v>554</v>
+      </c>
+      <c r="AB26" s="7">
+        <v>7311700</v>
+      </c>
       <c r="AC26" s="27">
         <f t="shared" si="5"/>
-        <v>-659</v>
+        <v>-105</v>
       </c>
       <c r="AD26" s="28">
         <f t="shared" si="5"/>
-        <v>-9900868</v>
+        <v>-2589168</v>
       </c>
       <c r="AE26" s="29">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.26150919293136721</v>
       </c>
       <c r="AG26" s="9" t="s">
         <v>12</v>
@@ -6275,15 +6385,15 @@
       <c r="AJ26" s="46"/>
       <c r="AK26" s="27">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-554</v>
       </c>
       <c r="AL26" s="28">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM26" s="29" t="e">
+        <v>-7311700</v>
+      </c>
+      <c r="AM26" s="29">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO26" s="9" t="s">
         <v>12</v>
@@ -6491,10 +6601,13 @@
       <c r="Z27" s="32" t="s">
         <v>19</v>
       </c>
+      <c r="AA27" s="1">
+        <v>5620</v>
+      </c>
       <c r="AB27" s="35"/>
       <c r="AC27" s="10">
         <f t="shared" si="5"/>
-        <v>-5245</v>
+        <v>375</v>
       </c>
       <c r="AD27" s="12">
         <f t="shared" si="5"/>
@@ -6514,7 +6627,7 @@
       <c r="AJ27" s="47"/>
       <c r="AK27" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-5620</v>
       </c>
       <c r="AL27" s="12">
         <f t="shared" si="7"/>
@@ -6964,18 +7077,23 @@
       <c r="Z29" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AB29" s="12"/>
+      <c r="AA29" s="10">
+        <v>88</v>
+      </c>
+      <c r="AB29" s="12">
+        <v>104849</v>
+      </c>
       <c r="AC29" s="10">
         <f t="shared" si="5"/>
-        <v>-91</v>
+        <v>-3</v>
       </c>
       <c r="AD29" s="12">
         <f t="shared" si="5"/>
-        <v>-107237</v>
+        <v>-2388</v>
       </c>
       <c r="AE29" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-2.226843346979121E-2</v>
       </c>
       <c r="AG29" s="14"/>
       <c r="AH29" s="13" t="s">
@@ -6985,15 +7103,15 @@
       <c r="AJ29" s="45"/>
       <c r="AK29" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-88</v>
       </c>
       <c r="AL29" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM29" s="11" t="e">
+        <v>-104849</v>
+      </c>
+      <c r="AM29" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO29" s="14"/>
       <c r="AP29" s="13" t="s">
@@ -7190,18 +7308,23 @@
       <c r="Z30" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AB30" s="12"/>
+      <c r="AA30" s="10">
+        <v>66</v>
+      </c>
+      <c r="AB30" s="12">
+        <v>81506</v>
+      </c>
       <c r="AC30" s="10">
         <f t="shared" si="5"/>
-        <v>-66</v>
+        <v>0</v>
       </c>
       <c r="AD30" s="12">
         <f t="shared" si="5"/>
-        <v>-60752</v>
+        <v>20754</v>
       </c>
       <c r="AE30" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>0.34161838293389518</v>
       </c>
       <c r="AG30" s="14"/>
       <c r="AH30" s="13" t="s">
@@ -7211,15 +7334,15 @@
       <c r="AJ30" s="45"/>
       <c r="AK30" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-66</v>
       </c>
       <c r="AL30" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM30" s="11" t="e">
+        <v>-81506</v>
+      </c>
+      <c r="AM30" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO30" s="14"/>
       <c r="AP30" s="13" t="s">
@@ -7416,18 +7539,23 @@
       <c r="Z31" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AB31" s="12"/>
+      <c r="AA31" s="10">
+        <v>24</v>
+      </c>
+      <c r="AB31" s="12">
+        <v>133676</v>
+      </c>
       <c r="AC31" s="10">
         <f t="shared" si="5"/>
-        <v>-22</v>
+        <v>2</v>
       </c>
       <c r="AD31" s="12">
         <f t="shared" si="5"/>
-        <v>-135981</v>
+        <v>-2305</v>
       </c>
       <c r="AE31" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-1.6950897551863863E-2</v>
       </c>
       <c r="AG31" s="14"/>
       <c r="AH31" s="13" t="s">
@@ -7437,15 +7565,15 @@
       <c r="AJ31" s="45"/>
       <c r="AK31" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="AL31" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM31" s="11" t="e">
+        <v>-133676</v>
+      </c>
+      <c r="AM31" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO31" s="14"/>
       <c r="AP31" s="13" t="s">
@@ -7642,18 +7770,23 @@
       <c r="Z32" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AB32" s="12"/>
+      <c r="AA32" s="10">
+        <v>7</v>
+      </c>
+      <c r="AB32" s="12">
+        <v>81714</v>
+      </c>
       <c r="AC32" s="10">
         <f t="shared" si="5"/>
-        <v>-13</v>
+        <v>-6</v>
       </c>
       <c r="AD32" s="12">
         <f t="shared" si="5"/>
-        <v>-186952</v>
+        <v>-105238</v>
       </c>
       <c r="AE32" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.56291454490992343</v>
       </c>
       <c r="AG32" s="14"/>
       <c r="AH32" s="13" t="s">
@@ -7663,15 +7796,15 @@
       <c r="AJ32" s="45"/>
       <c r="AK32" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="AL32" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM32" s="11" t="e">
+        <v>-81714</v>
+      </c>
+      <c r="AM32" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO32" s="14"/>
       <c r="AP32" s="13" t="s">
@@ -7868,7 +8001,12 @@
       <c r="Z33" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AB33" s="12"/>
+      <c r="AA33" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="12">
+        <v>0</v>
+      </c>
       <c r="AC33" s="10">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -8094,18 +8232,23 @@
       <c r="Z34" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AB34" s="12"/>
+      <c r="AA34" s="10">
+        <v>3</v>
+      </c>
+      <c r="AB34" s="12">
+        <v>90190</v>
+      </c>
       <c r="AC34" s="10">
         <f t="shared" si="5"/>
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AD34" s="12">
         <f t="shared" si="5"/>
-        <v>-24667</v>
+        <v>65523</v>
       </c>
       <c r="AE34" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>2.6563019418656504</v>
       </c>
       <c r="AG34" s="14"/>
       <c r="AH34" s="13" t="s">
@@ -8115,15 +8258,15 @@
       <c r="AJ34" s="45"/>
       <c r="AK34" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AL34" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM34" s="11" t="e">
+        <v>-90190</v>
+      </c>
+      <c r="AM34" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO34" s="14"/>
       <c r="AP34" s="13" t="s">
@@ -8320,18 +8463,23 @@
       <c r="Z35" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AB35" s="12"/>
+      <c r="AA35" s="10">
+        <v>6</v>
+      </c>
+      <c r="AB35" s="12">
+        <v>148952</v>
+      </c>
       <c r="AC35" s="10">
         <f t="shared" si="5"/>
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="AD35" s="12">
         <f t="shared" si="5"/>
-        <v>-81238</v>
+        <v>67714</v>
       </c>
       <c r="AE35" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>0.83352618232846698</v>
       </c>
       <c r="AG35" s="14"/>
       <c r="AH35" s="13" t="s">
@@ -8341,15 +8489,15 @@
       <c r="AJ35" s="45"/>
       <c r="AK35" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AL35" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM35" s="11" t="e">
+        <v>-148952</v>
+      </c>
+      <c r="AM35" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO35" s="14"/>
       <c r="AP35" s="13" t="s">
@@ -8546,18 +8694,23 @@
       <c r="Z36" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AB36" s="12"/>
+      <c r="AA36" s="10">
+        <v>66</v>
+      </c>
+      <c r="AB36" s="12">
+        <v>3433727</v>
+      </c>
       <c r="AC36" s="10">
         <f t="shared" si="5"/>
-        <v>-59</v>
+        <v>7</v>
       </c>
       <c r="AD36" s="12">
         <f t="shared" si="5"/>
-        <v>-2762000</v>
+        <v>671727</v>
       </c>
       <c r="AE36" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>0.24320311368573497</v>
       </c>
       <c r="AG36" s="14"/>
       <c r="AH36" s="13" t="s">
@@ -8567,15 +8720,15 @@
       <c r="AJ36" s="45"/>
       <c r="AK36" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-66</v>
       </c>
       <c r="AL36" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM36" s="11" t="e">
+        <v>-3433727</v>
+      </c>
+      <c r="AM36" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO36" s="14"/>
       <c r="AP36" s="13" t="s">
@@ -8773,19 +8926,23 @@
         <v>11</v>
       </c>
       <c r="Z37" s="9"/>
-      <c r="AA37" s="8"/>
-      <c r="AB37" s="7"/>
+      <c r="AA37" s="8">
+        <v>260</v>
+      </c>
+      <c r="AB37" s="7">
+        <v>4074614</v>
+      </c>
       <c r="AC37" s="27">
         <f t="shared" si="5"/>
-        <v>-255</v>
+        <v>5</v>
       </c>
       <c r="AD37" s="28">
         <f t="shared" si="5"/>
-        <v>-3358827</v>
+        <v>715787</v>
       </c>
       <c r="AE37" s="29">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>0.21310624214941704</v>
       </c>
       <c r="AG37" s="9" t="s">
         <v>11</v>
@@ -8795,15 +8952,15 @@
       <c r="AJ37" s="46"/>
       <c r="AK37" s="27">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-260</v>
       </c>
       <c r="AL37" s="28">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM37" s="29" t="e">
+        <v>-4074614</v>
+      </c>
+      <c r="AM37" s="29">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO37" s="9" t="s">
         <v>11</v>
@@ -9011,10 +9168,13 @@
       <c r="Z38" s="32" t="s">
         <v>19</v>
       </c>
+      <c r="AA38" s="1">
+        <v>2999</v>
+      </c>
       <c r="AB38" s="35"/>
       <c r="AC38" s="10">
         <f t="shared" si="5"/>
-        <v>-2648</v>
+        <v>351</v>
       </c>
       <c r="AD38" s="12">
         <f t="shared" si="5"/>
@@ -9034,7 +9194,7 @@
       <c r="AJ38" s="47"/>
       <c r="AK38" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-2999</v>
       </c>
       <c r="AL38" s="12">
         <f t="shared" si="7"/>
@@ -9483,18 +9643,23 @@
       <c r="Z40" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AB40" s="12"/>
+      <c r="AA40" s="10">
+        <v>161</v>
+      </c>
+      <c r="AB40" s="12">
+        <v>138747</v>
+      </c>
       <c r="AC40" s="10">
         <f t="shared" si="5"/>
-        <v>-173</v>
+        <v>-12</v>
       </c>
       <c r="AD40" s="12">
         <f t="shared" si="5"/>
-        <v>-152649</v>
+        <v>-13902</v>
       </c>
       <c r="AE40" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-9.1071674233044436E-2</v>
       </c>
       <c r="AG40" s="14"/>
       <c r="AH40" s="13" t="s">
@@ -9504,15 +9669,15 @@
       <c r="AJ40" s="45"/>
       <c r="AK40" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-161</v>
       </c>
       <c r="AL40" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM40" s="11" t="e">
+        <v>-138747</v>
+      </c>
+      <c r="AM40" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO40" s="14"/>
       <c r="AP40" s="13" t="s">
@@ -9709,18 +9874,23 @@
       <c r="Z41" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AB41" s="12"/>
+      <c r="AA41" s="10">
+        <v>79</v>
+      </c>
+      <c r="AB41" s="12">
+        <v>59067</v>
+      </c>
       <c r="AC41" s="10">
         <f t="shared" si="5"/>
-        <v>-100</v>
+        <v>-21</v>
       </c>
       <c r="AD41" s="12">
         <f t="shared" si="5"/>
-        <v>-118630</v>
+        <v>-59563</v>
       </c>
       <c r="AE41" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.50209053359184019</v>
       </c>
       <c r="AG41" s="14"/>
       <c r="AH41" s="13" t="s">
@@ -9730,15 +9900,15 @@
       <c r="AJ41" s="45"/>
       <c r="AK41" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-79</v>
       </c>
       <c r="AL41" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM41" s="11" t="e">
+        <v>-59067</v>
+      </c>
+      <c r="AM41" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO41" s="14"/>
       <c r="AP41" s="13" t="s">
@@ -9935,18 +10105,23 @@
       <c r="Z42" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AB42" s="12"/>
+      <c r="AA42" s="10">
+        <v>18</v>
+      </c>
+      <c r="AB42" s="12">
+        <v>104590</v>
+      </c>
       <c r="AC42" s="10">
         <f t="shared" si="5"/>
-        <v>-26</v>
+        <v>-8</v>
       </c>
       <c r="AD42" s="12">
         <f t="shared" si="5"/>
-        <v>-139181</v>
+        <v>-34591</v>
       </c>
       <c r="AE42" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.24853248647444695</v>
       </c>
       <c r="AG42" s="14"/>
       <c r="AH42" s="13" t="s">
@@ -9956,15 +10131,15 @@
       <c r="AJ42" s="45"/>
       <c r="AK42" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="AL42" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM42" s="11" t="e">
+        <v>-104590</v>
+      </c>
+      <c r="AM42" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO42" s="14"/>
       <c r="AP42" s="13" t="s">
@@ -10161,18 +10336,23 @@
       <c r="Z43" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AB43" s="12"/>
+      <c r="AA43" s="10">
+        <v>10</v>
+      </c>
+      <c r="AB43" s="12">
+        <v>116667</v>
+      </c>
       <c r="AC43" s="10">
         <f t="shared" si="5"/>
-        <v>-17</v>
+        <v>-7</v>
       </c>
       <c r="AD43" s="12">
         <f t="shared" si="5"/>
-        <v>-203143</v>
+        <v>-86476</v>
       </c>
       <c r="AE43" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.42569027729235071</v>
       </c>
       <c r="AG43" s="14"/>
       <c r="AH43" s="13" t="s">
@@ -10182,15 +10362,15 @@
       <c r="AJ43" s="45"/>
       <c r="AK43" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AL43" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM43" s="11" t="e">
+        <v>-116667</v>
+      </c>
+      <c r="AM43" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO43" s="14"/>
       <c r="AP43" s="13" t="s">
@@ -10387,18 +10567,23 @@
       <c r="Z44" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AB44" s="12"/>
+      <c r="AA44" s="10">
+        <v>2</v>
+      </c>
+      <c r="AB44" s="12">
+        <v>13080</v>
+      </c>
       <c r="AC44" s="10">
         <f t="shared" si="5"/>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="AD44" s="12">
         <f t="shared" si="5"/>
-        <v>-29360</v>
+        <v>-16280</v>
       </c>
       <c r="AE44" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.55449591280653954</v>
       </c>
       <c r="AG44" s="14"/>
       <c r="AH44" s="13" t="s">
@@ -10408,15 +10593,15 @@
       <c r="AJ44" s="45"/>
       <c r="AK44" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AL44" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM44" s="11" t="e">
+        <v>-13080</v>
+      </c>
+      <c r="AM44" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO44" s="14"/>
       <c r="AP44" s="13" t="s">
@@ -10616,18 +10801,23 @@
       <c r="Z45" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AB45" s="12"/>
+      <c r="AA45" s="10">
+        <v>7</v>
+      </c>
+      <c r="AB45" s="12">
+        <v>161238</v>
+      </c>
       <c r="AC45" s="10">
         <f t="shared" si="5"/>
-        <v>-6</v>
+        <v>1</v>
       </c>
       <c r="AD45" s="12">
         <f t="shared" si="5"/>
-        <v>-213899</v>
+        <v>-52661</v>
       </c>
       <c r="AE45" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.24619563438819256</v>
       </c>
       <c r="AG45" s="14"/>
       <c r="AH45" s="13" t="s">
@@ -10637,15 +10827,15 @@
       <c r="AJ45" s="45"/>
       <c r="AK45" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="AL45" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM45" s="11" t="e">
+        <v>-161238</v>
+      </c>
+      <c r="AM45" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO45" s="14"/>
       <c r="AP45" s="13" t="s">
@@ -10845,18 +11035,23 @@
       <c r="Z46" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AB46" s="12"/>
+      <c r="AA46" s="10">
+        <v>4</v>
+      </c>
+      <c r="AB46" s="12">
+        <v>87524</v>
+      </c>
       <c r="AC46" s="10">
         <f t="shared" si="5"/>
-        <v>-13</v>
+        <v>-9</v>
       </c>
       <c r="AD46" s="12">
         <f t="shared" si="5"/>
-        <v>-304952</v>
+        <v>-217428</v>
       </c>
       <c r="AE46" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.71299089692804118</v>
       </c>
       <c r="AG46" s="14"/>
       <c r="AH46" s="13" t="s">
@@ -10866,15 +11061,15 @@
       <c r="AJ46" s="45"/>
       <c r="AK46" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AL46" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM46" s="11" t="e">
+        <v>-87524</v>
+      </c>
+      <c r="AM46" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO46" s="14"/>
       <c r="AP46" s="13" t="s">
@@ -11074,18 +11269,23 @@
       <c r="Z47" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AB47" s="12"/>
+      <c r="AA47" s="10">
+        <v>67</v>
+      </c>
+      <c r="AB47" s="12">
+        <v>3432667</v>
+      </c>
       <c r="AC47" s="10">
         <f t="shared" si="5"/>
-        <v>-64</v>
+        <v>3</v>
       </c>
       <c r="AD47" s="12">
         <f t="shared" si="5"/>
-        <v>-3029143</v>
+        <v>403524</v>
       </c>
       <c r="AE47" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>0.13321391561903811</v>
       </c>
       <c r="AG47" s="14"/>
       <c r="AH47" s="13" t="s">
@@ -11095,15 +11295,15 @@
       <c r="AJ47" s="45"/>
       <c r="AK47" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-67</v>
       </c>
       <c r="AL47" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM47" s="11" t="e">
+        <v>-3432667</v>
+      </c>
+      <c r="AM47" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO47" s="14"/>
       <c r="AP47" s="13" t="s">
@@ -11304,19 +11504,23 @@
         <v>10</v>
       </c>
       <c r="Z48" s="9"/>
-      <c r="AA48" s="8"/>
-      <c r="AB48" s="7"/>
+      <c r="AA48" s="8">
+        <v>348</v>
+      </c>
+      <c r="AB48" s="7">
+        <v>4113580</v>
+      </c>
       <c r="AC48" s="27">
         <f t="shared" si="5"/>
-        <v>-403</v>
+        <v>-55</v>
       </c>
       <c r="AD48" s="28">
         <f t="shared" si="5"/>
-        <v>-4190957</v>
+        <v>-77377</v>
       </c>
       <c r="AE48" s="29">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-1.846284750714455E-2</v>
       </c>
       <c r="AG48" s="9" t="s">
         <v>10</v>
@@ -11326,15 +11530,15 @@
       <c r="AJ48" s="46"/>
       <c r="AK48" s="27">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-348</v>
       </c>
       <c r="AL48" s="28">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM48" s="29" t="e">
+        <v>-4113580</v>
+      </c>
+      <c r="AM48" s="29">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO48" s="9" t="s">
         <v>10</v>
@@ -12006,18 +12210,23 @@
       <c r="Z51" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AB51" s="12"/>
+      <c r="AA51" s="10">
+        <v>158</v>
+      </c>
+      <c r="AB51" s="12">
+        <v>146876</v>
+      </c>
       <c r="AC51" s="10">
         <f t="shared" si="5"/>
-        <v>-198</v>
+        <v>-40</v>
       </c>
       <c r="AD51" s="12">
         <f t="shared" si="5"/>
-        <v>-181024</v>
+        <v>-34148</v>
       </c>
       <c r="AE51" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.18863797065582463</v>
       </c>
       <c r="AG51" s="14"/>
       <c r="AH51" s="13" t="s">
@@ -12027,15 +12236,15 @@
       <c r="AJ51" s="45"/>
       <c r="AK51" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-158</v>
       </c>
       <c r="AL51" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM51" s="11" t="e">
+        <v>-146876</v>
+      </c>
+      <c r="AM51" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO51" s="14"/>
       <c r="AP51" s="13" t="s">
@@ -12232,18 +12441,23 @@
       <c r="Z52" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AB52" s="12"/>
+      <c r="AA52" s="10">
+        <v>75</v>
+      </c>
+      <c r="AB52" s="12">
+        <v>95476</v>
+      </c>
       <c r="AC52" s="10">
         <f t="shared" si="5"/>
-        <v>-76</v>
+        <v>-1</v>
       </c>
       <c r="AD52" s="12">
         <f t="shared" si="5"/>
-        <v>-79095</v>
+        <v>16381</v>
       </c>
       <c r="AE52" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>0.20710537960680195</v>
       </c>
       <c r="AG52" s="14"/>
       <c r="AH52" s="13" t="s">
@@ -12253,15 +12467,15 @@
       <c r="AJ52" s="45"/>
       <c r="AK52" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="AL52" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM52" s="11" t="e">
+        <v>-95476</v>
+      </c>
+      <c r="AM52" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO52" s="14"/>
       <c r="AP52" s="13" t="s">
@@ -12458,18 +12672,23 @@
       <c r="Z53" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AB53" s="12"/>
+      <c r="AA53" s="10">
+        <v>15</v>
+      </c>
+      <c r="AB53" s="12">
+        <v>79762</v>
+      </c>
       <c r="AC53" s="10">
         <f t="shared" si="5"/>
-        <v>-19</v>
+        <v>-4</v>
       </c>
       <c r="AD53" s="12">
         <f t="shared" si="5"/>
-        <v>-99057</v>
+        <v>-19295</v>
       </c>
       <c r="AE53" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.19478683990025944</v>
       </c>
       <c r="AG53" s="14"/>
       <c r="AH53" s="13" t="s">
@@ -12479,15 +12698,15 @@
       <c r="AJ53" s="45"/>
       <c r="AK53" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="AL53" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM53" s="11" t="e">
+        <v>-79762</v>
+      </c>
+      <c r="AM53" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO53" s="14"/>
       <c r="AP53" s="13" t="s">
@@ -12684,18 +12903,23 @@
       <c r="Z54" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="AB54" s="12"/>
+      <c r="AA54" s="10">
+        <v>7</v>
+      </c>
+      <c r="AB54" s="12">
+        <v>110286</v>
+      </c>
       <c r="AC54" s="10">
         <f t="shared" si="5"/>
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="AD54" s="12">
         <f t="shared" si="5"/>
-        <v>-247810</v>
+        <v>-137524</v>
       </c>
       <c r="AE54" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.55495742706105489</v>
       </c>
       <c r="AG54" s="14"/>
       <c r="AH54" s="13" t="s">
@@ -12705,15 +12929,15 @@
       <c r="AJ54" s="45"/>
       <c r="AK54" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="AL54" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM54" s="11" t="e">
+        <v>-110286</v>
+      </c>
+      <c r="AM54" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO54" s="14"/>
       <c r="AP54" s="13" t="s">
@@ -12910,18 +13134,23 @@
       <c r="Z55" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="AB55" s="12"/>
+      <c r="AA55" s="10">
+        <v>6</v>
+      </c>
+      <c r="AB55" s="12">
+        <v>41840</v>
+      </c>
       <c r="AC55" s="10">
         <f t="shared" si="5"/>
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="AD55" s="12">
         <f t="shared" si="5"/>
-        <v>-19650</v>
+        <v>22190</v>
       </c>
       <c r="AE55" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>1.1292620865139948</v>
       </c>
       <c r="AG55" s="14"/>
       <c r="AH55" s="13" t="s">
@@ -12931,15 +13160,15 @@
       <c r="AJ55" s="45"/>
       <c r="AK55" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AL55" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM55" s="11" t="e">
+        <v>-41840</v>
+      </c>
+      <c r="AM55" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO55" s="14"/>
       <c r="AP55" s="13" t="s">
@@ -13139,18 +13368,23 @@
       <c r="Z56" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AB56" s="12"/>
+      <c r="AA56" s="10">
+        <v>6</v>
+      </c>
+      <c r="AB56" s="12">
+        <v>213295</v>
+      </c>
       <c r="AC56" s="10">
         <f t="shared" si="5"/>
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="AD56" s="12">
         <f t="shared" si="5"/>
-        <v>-275524</v>
+        <v>-62229</v>
       </c>
       <c r="AE56" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.22585691264644822</v>
       </c>
       <c r="AG56" s="14"/>
       <c r="AH56" s="13" t="s">
@@ -13160,15 +13394,15 @@
       <c r="AJ56" s="45"/>
       <c r="AK56" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AL56" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM56" s="11" t="e">
+        <v>-213295</v>
+      </c>
+      <c r="AM56" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO56" s="14"/>
       <c r="AP56" s="13" t="s">
@@ -13368,18 +13602,23 @@
       <c r="Z57" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="AB57" s="12"/>
+      <c r="AA57" s="10">
+        <v>8</v>
+      </c>
+      <c r="AB57" s="12">
+        <v>186381</v>
+      </c>
       <c r="AC57" s="10">
         <f t="shared" si="5"/>
-        <v>-26</v>
+        <v>-18</v>
       </c>
       <c r="AD57" s="12">
         <f t="shared" si="5"/>
-        <v>-608952</v>
+        <v>-422571</v>
       </c>
       <c r="AE57" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.69393154140227797</v>
       </c>
       <c r="AG57" s="14"/>
       <c r="AH57" s="13" t="s">
@@ -13389,15 +13628,15 @@
       <c r="AJ57" s="45"/>
       <c r="AK57" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="AL57" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM57" s="11" t="e">
+        <v>-186381</v>
+      </c>
+      <c r="AM57" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO57" s="14"/>
       <c r="AP57" s="13" t="s">
@@ -13597,18 +13836,23 @@
       <c r="Z58" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AB58" s="12"/>
+      <c r="AA58" s="10">
+        <v>59</v>
+      </c>
+      <c r="AB58" s="12">
+        <v>3037238</v>
+      </c>
       <c r="AC58" s="10">
         <f t="shared" si="5"/>
-        <v>-112</v>
+        <v>-53</v>
       </c>
       <c r="AD58" s="12">
         <f t="shared" si="5"/>
-        <v>-4536000</v>
+        <v>-1498762</v>
       </c>
       <c r="AE58" s="11">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.33041490299823634</v>
       </c>
       <c r="AG58" s="14"/>
       <c r="AH58" s="13" t="s">
@@ -13618,15 +13862,15 @@
       <c r="AJ58" s="45"/>
       <c r="AK58" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-59</v>
       </c>
       <c r="AL58" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM58" s="11" t="e">
+        <v>-3037238</v>
+      </c>
+      <c r="AM58" s="11">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO58" s="14"/>
       <c r="AP58" s="13" t="s">
@@ -13827,19 +14071,23 @@
         <v>1</v>
       </c>
       <c r="Z59" s="9"/>
-      <c r="AA59" s="8"/>
-      <c r="AB59" s="7"/>
+      <c r="AA59" s="8">
+        <v>334</v>
+      </c>
+      <c r="AB59" s="7">
+        <v>3911154</v>
+      </c>
       <c r="AC59" s="27">
         <f t="shared" si="5"/>
-        <v>-461</v>
+        <v>-127</v>
       </c>
       <c r="AD59" s="28">
         <f t="shared" si="5"/>
-        <v>-6047112</v>
+        <v>-2135958</v>
       </c>
       <c r="AE59" s="29">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.35321952032639714</v>
       </c>
       <c r="AG59" s="9" t="s">
         <v>1</v>
@@ -13849,15 +14097,15 @@
       <c r="AJ59" s="46"/>
       <c r="AK59" s="27">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-334</v>
       </c>
       <c r="AL59" s="28">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM59" s="29" t="e">
+        <v>-3911154</v>
+      </c>
+      <c r="AM59" s="29">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO59" s="9" t="s">
         <v>1</v>
@@ -14063,19 +14311,23 @@
         <v>0</v>
       </c>
       <c r="Z60" s="4"/>
-      <c r="AA60" s="3"/>
-      <c r="AB60" s="2"/>
+      <c r="AA60" s="3">
+        <v>2521</v>
+      </c>
+      <c r="AB60" s="2">
+        <v>36077635</v>
+      </c>
       <c r="AC60" s="6">
         <f t="shared" si="5"/>
-        <v>-3259</v>
+        <v>-738</v>
       </c>
       <c r="AD60" s="5">
         <f t="shared" si="5"/>
-        <v>-48863744</v>
+        <v>-12786109</v>
       </c>
       <c r="AE60" s="30">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>-0.26166863104063415</v>
       </c>
       <c r="AG60" s="4" t="s">
         <v>0</v>
@@ -14085,15 +14337,15 @@
       <c r="AJ60" s="48"/>
       <c r="AK60" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-2521</v>
       </c>
       <c r="AL60" s="5">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM60" s="30" t="e">
+        <v>-36077635</v>
+      </c>
+      <c r="AM60" s="30">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="AO60" s="4" t="s">
         <v>0</v>
@@ -14245,7 +14497,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="111" operator="containsText" id="{84E91190-11E8-AE4A-9A8E-E0B241655290}">
+          <x14:cfRule type="containsText" priority="112" operator="containsText" id="{84E91190-11E8-AE4A-9A8E-E0B241655290}">
             <xm:f>NOT(ISERROR(SEARCH("-",E5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -14254,7 +14506,19 @@
               </font>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>M5:O60 U5:W60 AC5:AE60 AJ5:AM60 AS5:AU60 BA5:BC60 BI5:BK60 BQ5:BS60 BY5:CA60 CG5:CI60 CO5:CQ60 CW5:CY60 E7:G60</xm:sqref>
+          <xm:sqref>M5:O60 U5:W60 AJ5:AM60 AS5:AU60 BA5:BC60 BI5:BK60 BQ5:BS60 BY5:CA60 CG5:CI60 CO5:CQ60 CW5:CY60 E7:G60</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{15C2BE38-BA0E-C84C-BEFD-2FA0EAB30755}">
+            <xm:f>NOT(ISERROR(SEARCH("-",AC5)))</xm:f>
+            <xm:f>"-"</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFF0000"/>
+              </font>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>AC5:AE60</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/data/FY27Q1.xlsx
+++ b/data/FY27Q1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82DDDCB1-8A71-F449-8551-A6687578C1E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5234C8A5-CC1B-564B-AB92-878CC2C015FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15220" yWindow="780" windowWidth="18640" windowHeight="20260" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -1717,10 +1717,13 @@
       <c r="Z6" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="AA6" s="15">
+        <v>29</v>
+      </c>
       <c r="AB6" s="33"/>
       <c r="AC6" s="10">
         <f t="shared" si="5"/>
-        <v>-48</v>
+        <v>-19</v>
       </c>
       <c r="AD6" s="12">
         <f t="shared" si="5"/>
@@ -1738,7 +1741,7 @@
       <c r="AJ6" s="44"/>
       <c r="AK6" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-29</v>
       </c>
       <c r="AL6" s="12">
         <f t="shared" si="7"/>
@@ -4280,10 +4283,13 @@
       <c r="Z17" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="AA17" s="1">
+        <v>11</v>
+      </c>
       <c r="AB17" s="35"/>
       <c r="AC17" s="10">
         <f t="shared" si="5"/>
-        <v>-26</v>
+        <v>-15</v>
       </c>
       <c r="AD17" s="12">
         <f t="shared" si="5"/>
@@ -4301,7 +4307,7 @@
       <c r="AJ17" s="47"/>
       <c r="AK17" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="AL17" s="12">
         <f t="shared" si="7"/>
@@ -6847,10 +6853,13 @@
       <c r="Z28" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="AA28" s="1">
+        <v>4</v>
+      </c>
       <c r="AB28" s="35"/>
       <c r="AC28" s="10">
         <f t="shared" si="5"/>
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="AD28" s="12">
         <f t="shared" si="5"/>
@@ -6868,7 +6877,7 @@
       <c r="AJ28" s="47"/>
       <c r="AK28" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AL28" s="12">
         <f t="shared" si="7"/>
@@ -9414,10 +9423,13 @@
       <c r="Z39" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="AA39" s="1">
+        <v>12</v>
+      </c>
       <c r="AB39" s="35"/>
       <c r="AC39" s="10">
         <f t="shared" si="5"/>
-        <v>-3</v>
+        <v>9</v>
       </c>
       <c r="AD39" s="12">
         <f t="shared" si="5"/>
@@ -9435,7 +9447,7 @@
       <c r="AJ39" s="47"/>
       <c r="AK39" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="AL39" s="12">
         <f t="shared" si="7"/>
@@ -11980,10 +11992,13 @@
       <c r="Z50" s="32" t="s">
         <v>20</v>
       </c>
+      <c r="AA50" s="1">
+        <v>2</v>
+      </c>
       <c r="AB50" s="35"/>
       <c r="AC50" s="10">
         <f t="shared" si="5"/>
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="AD50" s="12">
         <f t="shared" si="5"/>
@@ -12001,7 +12016,7 @@
       <c r="AJ50" s="47"/>
       <c r="AK50" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AL50" s="12">
         <f t="shared" si="7"/>
